--- a/data/trans_orig/P15C-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P15C-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el principal daño o lesión producido en el último accidente en 2007</t>
+          <t>Población según el principal daño o lesión producido en el último accidente en 2007 (tasa de respuesta: 51,23%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1064</t>
+          <t>1036</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8974</t>
+          <t>8906</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>35,65%</t>
+          <t>35,38%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5425</t>
+          <t>4385</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>11,92%</t>
+          <t>9,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2058</t>
+          <t>2016</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11704</t>
+          <t>11432</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,55%</t>
+          <t>16,17%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>880</t>
+          <t>809</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7346</t>
+          <t>7564</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,22%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>29,18%</t>
+          <t>30,05%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1022</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8984</t>
+          <t>8918</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,73%</t>
+          <t>19,59%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3011</t>
+          <t>2855</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>12867</t>
+          <t>13200</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>18,67%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6532</t>
+          <t>6694</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>17181</t>
+          <t>16841</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>26,59%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>68,25%</t>
+          <t>66,9%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>25303</t>
+          <t>24800</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>37235</t>
+          <t>37078</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>55,58%</t>
+          <t>54,47%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>81,78%</t>
+          <t>81,44%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>35142</t>
+          <t>34910</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>51602</t>
+          <t>51357</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>49,7%</t>
+          <t>49,38%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>72,99%</t>
+          <t>72,64%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2524</t>
+          <t>2538</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>12362</t>
+          <t>11145</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,03%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>49,11%</t>
+          <t>44,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2930</t>
+          <t>2729</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12899</t>
+          <t>12942</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,33%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7518</t>
+          <t>7637</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>20999</t>
+          <t>20978</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>10,8%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>29,67%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1776</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>7,06%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,47 +1220,47 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
+          <t>834</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>7036</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>5,64%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>1,83%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>15,45%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>2567</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
           <t>827</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>7008</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>5,64%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>1,82%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>15,39%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>2567</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>827</t>
-        </is>
-      </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>6882</t>
+          <t>6225</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>9,73%</t>
+          <t>8,81%</t>
         </is>
       </c>
     </row>
@@ -1298,97 +1298,97 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>1776</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>7,06%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="R9" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>1934</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>4,25%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>1907</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>6120</t>
+          <t>5834</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18222</t>
+          <t>18593</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1543,12 +1543,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>23,21%</t>
+          <t>23,68%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>880</t>
+          <t>908</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6636</t>
+          <t>6959</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>18,94%</t>
+          <t>19,86%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>7866</t>
+          <t>8527</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>21621</t>
+          <t>22425</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>19,04%</t>
+          <t>19,75%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3176</t>
+          <t>3390</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>14931</t>
+          <t>15504</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,05%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1681,7 +1681,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>5511</t>
+          <t>4602</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>4283</t>
+          <t>4253</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>17252</t>
+          <t>17047</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,01%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>25067</t>
+          <t>25171</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>43131</t>
+          <t>42617</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>32,06%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>54,94%</t>
+          <t>54,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>16160</t>
+          <t>15502</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>27323</t>
+          <t>27053</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>46,11%</t>
+          <t>44,24%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>77,97%</t>
+          <t>77,2%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>45028</t>
+          <t>44207</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>66414</t>
+          <t>66053</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>39,66%</t>
+          <t>38,93%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>58,49%</t>
+          <t>58,17%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>12325</t>
+          <t>11974</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>27660</t>
+          <t>27254</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,25%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>35,23%</t>
+          <t>34,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3071</t>
+          <t>3130</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>12261</t>
+          <t>13204</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>34,99%</t>
+          <t>37,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>17763</t>
+          <t>18603</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>36103</t>
+          <t>37427</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>16,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>31,8%</t>
+          <t>32,96%</t>
         </is>
       </c>
     </row>
@@ -1980,12 +1980,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2922</t>
+          <t>2871</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>12690</t>
+          <t>12808</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1995,12 +1995,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2020,7 +2020,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>7408</t>
+          <t>6255</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>17,85%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2050,12 +2050,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>4615</t>
+          <t>4611</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>15207</t>
+          <t>15532</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2070,7 +2070,7 @@
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>13,39%</t>
+          <t>13,68%</t>
         </is>
       </c>
     </row>
@@ -2093,97 +2093,97 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1953</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>2,49%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>1911</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>5,45%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>1961</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2323,97 +2323,97 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>1934</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>2050</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr">
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>5515</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>14,61%</t>
+        </is>
+      </c>
+      <c r="O18" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>11,15%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
+      <c r="P18" s="2" t="inlineStr">
+        <is>
+          <t>41,66%</t>
+        </is>
+      </c>
+      <c r="Q18" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K18" s="2" t="inlineStr">
+      <c r="R18" s="2" t="inlineStr">
         <is>
           <t>1934</t>
         </is>
       </c>
-      <c r="L18" s="2" t="inlineStr">
+      <c r="S18" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>5437</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>14,61%</t>
-        </is>
-      </c>
-      <c r="O18" s="2" t="inlineStr">
+      <c r="T18" s="2" t="inlineStr">
+        <is>
+          <t>5948</t>
+        </is>
+      </c>
+      <c r="U18" s="2" t="inlineStr">
+        <is>
+          <t>6,11%</t>
+        </is>
+      </c>
+      <c r="V18" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P18" s="2" t="inlineStr">
-        <is>
-          <t>41,08%</t>
-        </is>
-      </c>
-      <c r="Q18" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R18" s="2" t="inlineStr">
-        <is>
-          <t>1934</t>
-        </is>
-      </c>
-      <c r="S18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T18" s="2" t="inlineStr">
-        <is>
-          <t>6445</t>
-        </is>
-      </c>
-      <c r="U18" s="2" t="inlineStr">
-        <is>
-          <t>6,11%</t>
-        </is>
-      </c>
-      <c r="V18" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>20,38%</t>
+          <t>18,8%</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2441,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5634</t>
+          <t>5873</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>30,63%</t>
+          <t>31,92%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,62 +2471,62 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P19" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q19" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R19" s="2" t="inlineStr">
+        <is>
+          <t>1114</t>
+        </is>
+      </c>
+      <c r="S19" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>1920</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
+      <c r="T19" s="2" t="inlineStr">
+        <is>
+          <t>6344</t>
+        </is>
+      </c>
+      <c r="U19" s="2" t="inlineStr">
+        <is>
+          <t>3,52%</t>
+        </is>
+      </c>
+      <c r="V19" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P19" s="2" t="inlineStr">
-        <is>
-          <t>14,51%</t>
-        </is>
-      </c>
-      <c r="Q19" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R19" s="2" t="inlineStr">
-        <is>
-          <t>1114</t>
-        </is>
-      </c>
-      <c r="S19" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" s="2" t="inlineStr">
-        <is>
-          <t>5719</t>
-        </is>
-      </c>
-      <c r="U19" s="2" t="inlineStr">
-        <is>
-          <t>3,52%</t>
-        </is>
-      </c>
-      <c r="V19" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>20,06%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>8108</t>
+          <t>8642</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>16690</t>
+          <t>17236</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>44,07%</t>
+          <t>46,98%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>93,69%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>4259</t>
+          <t>3700</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>11412</t>
+          <t>11239</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>32,18%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>86,22%</t>
+          <t>84,91%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>15073</t>
+          <t>14911</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>25938</t>
+          <t>25838</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>47,65%</t>
+          <t>47,14%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>82,0%</t>
+          <t>81,68%</t>
         </is>
       </c>
     </row>
@@ -2667,7 +2667,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7883</t>
+          <t>8171</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2682,7 +2682,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>42,85%</t>
+          <t>44,41%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2697,12 +2697,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>954</t>
+          <t>962</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>7816</t>
+          <t>7864</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2712,12 +2712,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>7,21%</t>
+          <t>7,26%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>59,05%</t>
+          <t>59,41%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2732,12 +2732,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1641</t>
+          <t>1586</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>12093</t>
+          <t>11882</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2747,12 +2747,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>5,19%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>38,23%</t>
+          <t>37,56%</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4320</t>
+          <t>3977</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>23,48%</t>
+          <t>21,62%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2810,62 +2810,62 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>949</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>1920</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>4680</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>3,0%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>14,51%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>949</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>5091</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>3,0%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>14,79%</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>6164</t>
+          <t>4586</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2908,7 +2908,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>33,51%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2923,62 +2923,62 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R23" s="2" t="inlineStr">
+        <is>
+          <t>1038</t>
+        </is>
+      </c>
+      <c r="S23" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>1920</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>8071</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
+        <is>
+          <t>3,28%</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>14,51%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>1038</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>4875</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>3,28%</t>
-        </is>
-      </c>
-      <c r="V23" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>25,51%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>8903</t>
+          <t>9081</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>22682</t>
+          <t>23218</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,29%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2120</t>
+          <t>2002</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>12238</t>
+          <t>12789</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,26%</t>
+          <t>2,13%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>14089</t>
+          <t>13336</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>30574</t>
+          <t>31008</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>14,16%</t>
+          <t>14,36%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>6342</t>
+          <t>6730</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>20107</t>
+          <t>21069</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,51%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>16,47%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1038</t>
+          <t>1090</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>10986</t>
+          <t>10346</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>9357</t>
+          <t>9727</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>26272</t>
+          <t>24545</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>11,37%</t>
         </is>
       </c>
     </row>
@@ -3344,12 +3344,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>48498</t>
+          <t>48247</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>70355</t>
+          <t>71006</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3359,12 +3359,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>39,73%</t>
+          <t>39,52%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>57,63%</t>
+          <t>58,17%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>51822</t>
+          <t>51596</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>70273</t>
+          <t>70832</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3394,12 +3394,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>55,24%</t>
+          <t>55,0%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>74,91%</t>
+          <t>75,51%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>105488</t>
+          <t>104205</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>135598</t>
+          <t>133501</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3429,12 +3429,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>48,86%</t>
+          <t>48,27%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>62,81%</t>
+          <t>61,84%</t>
         </is>
       </c>
     </row>
@@ -3457,12 +3457,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>18946</t>
+          <t>19376</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>38256</t>
+          <t>37915</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3472,12 +3472,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,87%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>31,34%</t>
+          <t>31,06%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>10325</t>
+          <t>11096</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>25815</t>
+          <t>27007</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3507,12 +3507,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11,01%</t>
+          <t>11,83%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>27,52%</t>
+          <t>28,79%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>32991</t>
+          <t>33184</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>57482</t>
+          <t>58240</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3542,12 +3542,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,37%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>26,63%</t>
+          <t>26,98%</t>
         </is>
       </c>
     </row>
@@ -3570,12 +3570,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3017</t>
+          <t>3738</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>13553</t>
+          <t>13687</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3585,12 +3585,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>11,1%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1745</t>
+          <t>1709</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>9870</t>
+          <t>10156</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3620,12 +3620,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6588</t>
+          <t>6603</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>19603</t>
+          <t>19526</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3655,12 +3655,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,06%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>9,08%</t>
+          <t>9,04%</t>
         </is>
       </c>
     </row>
@@ -3688,7 +3688,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>6897</t>
+          <t>6171</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3703,7 +3703,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,05%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3718,62 +3718,62 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>1038</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>1975</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>6038</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>0,48%</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O30" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P30" s="2" t="inlineStr">
-        <is>
-          <t>2,11%</t>
-        </is>
-      </c>
-      <c r="Q30" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R30" s="2" t="inlineStr">
-        <is>
-          <t>1038</t>
-        </is>
-      </c>
-      <c r="S30" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T30" s="2" t="inlineStr">
-        <is>
-          <t>5932</t>
-        </is>
-      </c>
-      <c r="U30" s="2" t="inlineStr">
-        <is>
-          <t>0,48%</t>
-        </is>
-      </c>
-      <c r="V30" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,8%</t>
         </is>
       </c>
     </row>
@@ -3949,7 +3949,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el principal daño o lesión producido en el último accidente en 2012</t>
+          <t>Población según el principal daño o lesión producido en el último accidente en 2012 (tasa de respuesta: 98,84%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1088</t>
+          <t>1078</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9805</t>
+          <t>10323</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2077</t>
+          <t>2050</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11681</t>
+          <t>12051</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5078</t>
+          <t>4381</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17226</t>
+          <t>17377</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,13%</t>
+          <t>9,21%</t>
         </is>
       </c>
     </row>
@@ -4257,12 +4257,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1682</t>
+          <t>1458</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9505</t>
+          <t>9255</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,55%</t>
+          <t>12,22%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2075</t>
+          <t>2914</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11984</t>
+          <t>12176</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,84%</t>
+          <t>2,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4327,12 +4327,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5608</t>
+          <t>5651</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>18457</t>
+          <t>17716</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4342,12 +4342,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,97%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,78%</t>
+          <t>9,39%</t>
         </is>
       </c>
     </row>
@@ -4370,12 +4370,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>35645</t>
+          <t>35171</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>53322</t>
+          <t>53632</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4385,12 +4385,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>47,05%</t>
+          <t>46,43%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>70,39%</t>
+          <t>70,8%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4405,12 +4405,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>51895</t>
+          <t>51197</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>72943</t>
+          <t>72419</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>45,95%</t>
+          <t>45,33%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>64,59%</t>
+          <t>64,12%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>93324</t>
+          <t>93517</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>121183</t>
+          <t>121536</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>49,46%</t>
+          <t>49,56%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>64,22%</t>
+          <t>64,41%</t>
         </is>
       </c>
     </row>
@@ -4483,12 +4483,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8218</t>
+          <t>8367</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>22627</t>
+          <t>23185</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,85%</t>
+          <t>11,04%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,87%</t>
+          <t>30,61%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4518,12 +4518,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>10669</t>
+          <t>11498</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>26689</t>
+          <t>27384</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4533,12 +4533,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,63%</t>
+          <t>24,25%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4553,12 +4553,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>22694</t>
+          <t>22876</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>44428</t>
+          <t>44636</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4568,12 +4568,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,03%</t>
+          <t>12,12%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,55%</t>
+          <t>23,66%</t>
         </is>
       </c>
     </row>
@@ -4596,12 +4596,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3214</t>
+          <t>3281</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>14696</t>
+          <t>14578</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4611,12 +4611,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,24%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4631,12 +4631,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>14125</t>
+          <t>13816</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>31707</t>
+          <t>30624</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4646,12 +4646,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12,51%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>28,07%</t>
+          <t>27,12%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4666,12 +4666,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>19951</t>
+          <t>20193</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>39804</t>
+          <t>39938</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,7%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>21,09%</t>
+          <t>21,17%</t>
         </is>
       </c>
     </row>
@@ -4709,97 +4709,97 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>2043</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>2,7%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="R9" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>2005</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>1,77%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>2034</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -4939,12 +4939,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5623</t>
+          <t>5511</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19735</t>
+          <t>19019</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4954,12 +4954,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,1%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4974,12 +4974,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4871</t>
+          <t>4952</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>17506</t>
+          <t>17679</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4989,12 +4989,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>15,26%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5009,12 +5009,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>12781</t>
+          <t>13134</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>30142</t>
+          <t>30890</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5024,12 +5024,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,43%</t>
         </is>
       </c>
     </row>
@@ -5052,12 +5052,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8760</t>
+          <t>8383</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>25185</t>
+          <t>24358</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5067,12 +5067,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,88%</t>
+          <t>13,42%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4379</t>
+          <t>4261</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>16673</t>
+          <t>16670</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5102,7 +5102,7 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>16768</t>
+          <t>16277</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>37887</t>
+          <t>36343</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5137,12 +5137,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,66%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,27%</t>
         </is>
       </c>
     </row>
@@ -5165,12 +5165,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>107689</t>
+          <t>106891</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>134361</t>
+          <t>132479</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5180,12 +5180,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>59,35%</t>
+          <t>58,91%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>74,05%</t>
+          <t>73,01%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5200,12 +5200,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>48993</t>
+          <t>49348</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>71047</t>
+          <t>70198</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5215,12 +5215,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>42,71%</t>
+          <t>43,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>61,93%</t>
+          <t>61,19%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5235,12 +5235,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>163036</t>
+          <t>163421</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>197041</t>
+          <t>198124</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5250,12 +5250,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>55,05%</t>
+          <t>55,18%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>66,53%</t>
+          <t>66,89%</t>
         </is>
       </c>
     </row>
@@ -5278,12 +5278,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>14323</t>
+          <t>14489</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>33171</t>
+          <t>34058</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5293,12 +5293,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,89%</t>
+          <t>7,98%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>18,28%</t>
+          <t>18,77%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5313,12 +5313,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>11609</t>
+          <t>11447</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>27964</t>
+          <t>27755</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>9,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>24,19%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>29874</t>
+          <t>29638</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>54286</t>
+          <t>54512</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,09%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>18,41%</t>
         </is>
       </c>
     </row>
@@ -5391,12 +5391,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5168</t>
+          <t>5235</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>18555</t>
+          <t>17636</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5406,12 +5406,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>10,23%</t>
+          <t>9,72%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5426,12 +5426,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>10381</t>
+          <t>9642</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>26550</t>
+          <t>25413</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>23,14%</t>
+          <t>22,15%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>17075</t>
+          <t>17802</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>38748</t>
+          <t>39206</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>6,01%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>13,08%</t>
+          <t>13,24%</t>
         </is>
       </c>
     </row>
@@ -5509,7 +5509,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4543</t>
+          <t>4779</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5524,7 +5524,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5539,62 +5539,62 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>1010</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>2017</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>5741</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>0,34%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>1,76%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>1010</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>5070</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,34%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>1,94%</t>
         </is>
       </c>
     </row>
@@ -5739,7 +5739,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4555</t>
+          <t>4885</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5774,7 +5774,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>7509</t>
+          <t>8255</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5789,7 +5789,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>27,08%</t>
+          <t>29,77%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5809,7 +5809,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>9584</t>
+          <t>10058</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>17,82%</t>
+          <t>18,7%</t>
         </is>
       </c>
     </row>
@@ -5852,7 +5852,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4672</t>
+          <t>4208</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5867,7 +5867,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>16,15%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5887,7 +5887,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5278</t>
+          <t>5665</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5902,7 +5902,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>20,43%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5922,7 +5922,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6123</t>
+          <t>6298</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5937,7 +5937,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,71%</t>
         </is>
       </c>
     </row>
@@ -5960,12 +5960,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>16406</t>
+          <t>16647</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>24218</t>
+          <t>24213</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5975,12 +5975,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>62,97%</t>
+          <t>63,89%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,95%</t>
+          <t>92,93%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5995,12 +5995,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>11917</t>
+          <t>12323</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>23553</t>
+          <t>23458</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6010,12 +6010,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>42,98%</t>
+          <t>44,44%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>84,93%</t>
+          <t>84,59%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6030,12 +6030,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>31738</t>
+          <t>32462</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>45861</t>
+          <t>45619</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6045,12 +6045,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>59,01%</t>
+          <t>60,36%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>85,27%</t>
+          <t>84,82%</t>
         </is>
       </c>
     </row>
@@ -6073,12 +6073,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>853</t>
+          <t>887</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>6949</t>
+          <t>7106</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>26,67%</t>
+          <t>27,27%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6113,7 +6113,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>6389</t>
+          <t>6397</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6128,7 +6128,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>23,07%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6143,12 +6143,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1226</t>
+          <t>978</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>10320</t>
+          <t>10400</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6158,12 +6158,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>19,34%</t>
         </is>
       </c>
     </row>
@@ -6186,12 +6186,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1908</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -6201,12 +6201,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -6221,12 +6221,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1827</t>
+          <t>1051</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>11417</t>
+          <t>10539</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6236,12 +6236,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>41,17%</t>
+          <t>38,0%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6256,12 +6256,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1014</t>
+          <t>1010</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>11581</t>
+          <t>12457</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6276,7 +6276,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>21,53%</t>
+          <t>23,16%</t>
         </is>
       </c>
     </row>
@@ -6299,97 +6299,97 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>1908</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>7,32%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K23" s="2" t="inlineStr">
+      <c r="R23" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>2111</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>7,61%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>2057</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -6529,12 +6529,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>9630</t>
+          <t>9596</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>25885</t>
+          <t>26888</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,39%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,14%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6564,12 +6564,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>10057</t>
+          <t>10097</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>27683</t>
+          <t>26521</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6579,12 +6579,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,94%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,38%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6599,12 +6599,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>22969</t>
+          <t>23840</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>47185</t>
+          <t>46343</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6614,12 +6614,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,6%</t>
         </is>
       </c>
     </row>
@@ -6642,12 +6642,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>13359</t>
+          <t>13318</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>30820</t>
+          <t>30970</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6657,12 +6657,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>4,72%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>10,88%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6677,12 +6677,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>9404</t>
+          <t>10076</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>25788</t>
+          <t>25065</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6692,12 +6692,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6712,12 +6712,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>27075</t>
+          <t>25889</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>50070</t>
+          <t>49836</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6727,12 +6727,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,81%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,25%</t>
         </is>
       </c>
     </row>
@@ -6755,12 +6755,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>170747</t>
+          <t>170334</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>202327</t>
+          <t>204292</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6770,12 +6770,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>60,28%</t>
+          <t>60,13%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>71,43%</t>
+          <t>72,12%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6790,12 +6790,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>123919</t>
+          <t>123343</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>157076</t>
+          <t>157410</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6805,12 +6805,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>48,52%</t>
+          <t>48,3%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>61,51%</t>
+          <t>61,64%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -6825,12 +6825,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>307019</t>
+          <t>305430</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>353038</t>
+          <t>352370</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>57,0%</t>
+          <t>56,7%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>65,54%</t>
+          <t>65,42%</t>
         </is>
       </c>
     </row>
@@ -6868,12 +6868,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>29234</t>
+          <t>29346</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>52763</t>
+          <t>53193</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6883,12 +6883,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>10,32%</t>
+          <t>10,36%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>18,63%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>28329</t>
+          <t>28093</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>50843</t>
+          <t>51215</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6918,12 +6918,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11,09%</t>
+          <t>11,0%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>19,91%</t>
+          <t>20,05%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6938,12 +6938,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>63933</t>
+          <t>62737</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>96461</t>
+          <t>96960</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6953,12 +6953,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,65%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>17,91%</t>
+          <t>18,0%</t>
         </is>
       </c>
     </row>
@@ -6981,12 +6981,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>10663</t>
+          <t>10384</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>27305</t>
+          <t>27421</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6996,12 +6996,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,76%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,68%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7016,12 +7016,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>31349</t>
+          <t>29599</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>55809</t>
+          <t>54510</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7031,12 +7031,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>12,28%</t>
+          <t>11,59%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>21,34%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7051,12 +7051,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>46035</t>
+          <t>46438</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>77853</t>
+          <t>77053</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7066,12 +7066,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>14,45%</t>
+          <t>14,3%</t>
         </is>
       </c>
     </row>
@@ -7099,7 +7099,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>5017</t>
+          <t>5081</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7114,7 +7114,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7129,62 +7129,62 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R30" s="2" t="inlineStr">
+        <is>
+          <t>1010</t>
+        </is>
+      </c>
+      <c r="S30" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>2042</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>4800</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>0,19%</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O30" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P30" s="2" t="inlineStr">
-        <is>
-          <t>0,8%</t>
-        </is>
-      </c>
-      <c r="Q30" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R30" s="2" t="inlineStr">
-        <is>
-          <t>1010</t>
-        </is>
-      </c>
-      <c r="S30" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T30" s="2" t="inlineStr">
-        <is>
-          <t>4307</t>
-        </is>
-      </c>
-      <c r="U30" s="2" t="inlineStr">
-        <is>
-          <t>0,19%</t>
-        </is>
-      </c>
-      <c r="V30" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,89%</t>
         </is>
       </c>
     </row>
@@ -7360,7 +7360,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el principal daño o lesión producido en el último accidente en 2016</t>
+          <t>Población según el principal daño o lesión producido en el último accidente en 2016 (tasa de respuesta: 98,36%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -7555,12 +7555,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1010</t>
+          <t>940</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8709</t>
+          <t>8531</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7570,12 +7570,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,4%</t>
+          <t>19,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7595,7 +7595,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>7044</t>
+          <t>6557</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7610,7 +7610,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,05%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7625,12 +7625,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1870</t>
+          <t>1803</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10614</t>
+          <t>10823</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7640,12 +7640,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,59%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>9,22%</t>
         </is>
       </c>
     </row>
@@ -7668,12 +7668,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2043</t>
+          <t>2012</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>11804</t>
+          <t>10818</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7683,12 +7683,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,55%</t>
+          <t>4,48%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>26,29%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7703,12 +7703,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2273</t>
+          <t>2316</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>13419</t>
+          <t>12874</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7718,12 +7718,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>17,77%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6860</t>
+          <t>6851</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>20143</t>
+          <t>19740</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>17,17%</t>
+          <t>16,82%</t>
         </is>
       </c>
     </row>
@@ -7781,12 +7781,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>17596</t>
+          <t>17689</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>29848</t>
+          <t>29683</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7796,12 +7796,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>39,19%</t>
+          <t>39,4%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>66,48%</t>
+          <t>66,11%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7816,12 +7816,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>39946</t>
+          <t>39966</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>58055</t>
+          <t>57263</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7831,12 +7831,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>55,14%</t>
+          <t>55,17%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>80,14%</t>
+          <t>79,05%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7851,12 +7851,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>62777</t>
+          <t>62137</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>84354</t>
+          <t>83685</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>53,5%</t>
+          <t>52,96%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>71,89%</t>
+          <t>71,32%</t>
         </is>
       </c>
     </row>
@@ -7894,12 +7894,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5596</t>
+          <t>5497</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16883</t>
+          <t>16469</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7909,12 +7909,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>37,6%</t>
+          <t>36,68%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7929,12 +7929,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>8473</t>
+          <t>7918</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>23956</t>
+          <t>23862</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7944,12 +7944,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>10,93%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>33,07%</t>
+          <t>32,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7964,12 +7964,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>16508</t>
+          <t>16728</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>35281</t>
+          <t>35876</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7979,12 +7979,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,07%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>30,58%</t>
         </is>
       </c>
     </row>
@@ -8012,7 +8012,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5577</t>
+          <t>5569</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8027,7 +8027,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>12,42%</t>
+          <t>12,4%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8042,62 +8042,62 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R8" s="2" t="inlineStr">
+        <is>
+          <t>973</t>
+        </is>
+      </c>
+      <c r="S8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>2236</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>5392</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>0,83%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O8" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>3,09%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>973</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>5434</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>0,83%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,6%</t>
         </is>
       </c>
     </row>
@@ -8120,97 +8120,97 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>1752</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>3,9%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="O9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="R9" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>2236</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
+      <c r="S9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O9" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>3,09%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>2045</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -8350,12 +8350,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4081</t>
+          <t>4506</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>16975</t>
+          <t>17349</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8365,12 +8365,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,39%</t>
+          <t>14,71%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8385,12 +8385,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5097</t>
+          <t>5095</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>17529</t>
+          <t>17581</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8405,7 +8405,7 @@
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>20,48%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8420,12 +8420,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>11040</t>
+          <t>11386</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>28529</t>
+          <t>29821</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8435,12 +8435,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,63%</t>
         </is>
       </c>
     </row>
@@ -8463,12 +8463,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3462</t>
+          <t>3468</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>16210</t>
+          <t>15849</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,74%</t>
+          <t>13,44%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8498,12 +8498,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2047</t>
+          <t>2897</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>12291</t>
+          <t>11645</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8513,12 +8513,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,32%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8533,12 +8533,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>8116</t>
+          <t>8374</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>23617</t>
+          <t>23429</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8548,12 +8548,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,98%</t>
+          <t>4,11%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>11,5%</t>
         </is>
       </c>
     </row>
@@ -8576,12 +8576,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>66039</t>
+          <t>64636</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>86435</t>
+          <t>86092</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>55,98%</t>
+          <t>54,79%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>73,27%</t>
+          <t>72,98%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8611,12 +8611,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>40549</t>
+          <t>40192</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>59093</t>
+          <t>59059</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8626,12 +8626,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>47,24%</t>
+          <t>46,82%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>68,84%</t>
+          <t>68,8%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8646,12 +8646,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>112144</t>
+          <t>112802</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>139766</t>
+          <t>140438</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8661,12 +8661,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>55,02%</t>
+          <t>55,35%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>68,58%</t>
+          <t>68,91%</t>
         </is>
       </c>
     </row>
@@ -8689,12 +8689,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>14004</t>
+          <t>13123</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>31532</t>
+          <t>30616</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8704,12 +8704,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,87%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>26,73%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8724,12 +8724,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>7037</t>
+          <t>6373</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>20853</t>
+          <t>20642</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8739,12 +8739,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,05%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8759,12 +8759,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>23915</t>
+          <t>23564</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>45771</t>
+          <t>45416</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8774,12 +8774,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>11,73%</t>
+          <t>11,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,28%</t>
         </is>
       </c>
     </row>
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1024</t>
+          <t>1042</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9801</t>
+          <t>9347</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8817,12 +8817,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>8,31%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8837,12 +8837,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1525</t>
+          <t>1198</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>11328</t>
+          <t>11237</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8852,12 +8852,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>13,2%</t>
+          <t>13,09%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -8872,12 +8872,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>3998</t>
+          <t>4037</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>16267</t>
+          <t>17442</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8887,12 +8887,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,56%</t>
         </is>
       </c>
     </row>
@@ -8915,97 +8915,97 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>2529</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>2001</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>7807</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>2,95%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>1,7%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>9,09%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>2529</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>8807</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>2,95%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>9330</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>1,24%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>10,26%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>2529</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>9083</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>1,24%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,58%</t>
         </is>
       </c>
     </row>
@@ -9145,12 +9145,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1978</t>
+          <t>1916</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>11538</t>
+          <t>11768</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9160,12 +9160,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>37,47%</t>
+          <t>38,21%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9185,7 +9185,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6289</t>
+          <t>6318</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9200,7 +9200,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9215,12 +9215,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3473</t>
+          <t>3003</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>15094</t>
+          <t>13978</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9230,12 +9230,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>4,86%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>24,42%</t>
+          <t>22,62%</t>
         </is>
       </c>
     </row>
@@ -9263,7 +9263,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6071</t>
+          <t>6606</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>19,71%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9298,7 +9298,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>6891</t>
+          <t>8209</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9313,7 +9313,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>22,22%</t>
+          <t>26,48%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9328,12 +9328,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1121</t>
+          <t>1042</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>9968</t>
+          <t>10244</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9343,12 +9343,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,13%</t>
+          <t>16,58%</t>
         </is>
       </c>
     </row>
@@ -9371,12 +9371,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>10123</t>
+          <t>10077</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>21774</t>
+          <t>21553</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9386,12 +9386,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>32,87%</t>
+          <t>32,72%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>70,7%</t>
+          <t>69,99%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9406,12 +9406,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>14303</t>
+          <t>13881</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>25579</t>
+          <t>25463</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9421,12 +9421,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>46,13%</t>
+          <t>44,77%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>82,49%</t>
+          <t>82,12%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9441,12 +9441,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>28251</t>
+          <t>27047</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>43910</t>
+          <t>44414</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9456,12 +9456,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>45,71%</t>
+          <t>43,76%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>71,05%</t>
+          <t>71,86%</t>
         </is>
       </c>
     </row>
@@ -9484,12 +9484,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2197</t>
+          <t>2388</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>13359</t>
+          <t>12478</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9499,12 +9499,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,76%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>43,38%</t>
+          <t>40,52%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9519,12 +9519,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2222</t>
+          <t>2191</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>13213</t>
+          <t>13343</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9534,12 +9534,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,07%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>42,61%</t>
+          <t>43,03%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9554,12 +9554,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>6547</t>
+          <t>6847</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>20740</t>
+          <t>22797</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9569,12 +9569,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>10,59%</t>
+          <t>11,08%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>33,56%</t>
+          <t>36,89%</t>
         </is>
       </c>
     </row>
@@ -9602,7 +9602,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4830</t>
+          <t>4842</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9617,7 +9617,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,72%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9632,47 +9632,47 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>868</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>2038</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>6,57%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>868</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4611</t>
+          <t>4613</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9710,97 +9710,97 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>2096</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>6,81%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K23" s="2" t="inlineStr">
+      <c r="R23" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>2038</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>6,57%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>2112</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -9940,12 +9940,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>11095</t>
+          <t>11049</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>28021</t>
+          <t>27999</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9955,12 +9955,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9975,12 +9975,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>7410</t>
+          <t>7001</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>21417</t>
+          <t>21579</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9990,12 +9990,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>3,7%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,31%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10010,12 +10010,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>21987</t>
+          <t>21878</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>44696</t>
+          <t>43522</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10025,12 +10025,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,71%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>11,67%</t>
+          <t>11,36%</t>
         </is>
       </c>
     </row>
@@ -10053,12 +10053,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>9295</t>
+          <t>9210</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>26130</t>
+          <t>25467</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10068,12 +10068,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,76%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -10088,12 +10088,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>8126</t>
+          <t>8542</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>23965</t>
+          <t>25203</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -10103,12 +10103,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>12,66%</t>
+          <t>13,31%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -10123,12 +10123,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>20768</t>
+          <t>21815</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>41526</t>
+          <t>44356</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,7%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>11,58%</t>
         </is>
       </c>
     </row>
@@ -10166,12 +10166,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>102345</t>
+          <t>101895</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>129152</t>
+          <t>129307</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -10181,12 +10181,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>52,85%</t>
+          <t>52,62%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>66,69%</t>
+          <t>66,77%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -10201,12 +10201,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>106089</t>
+          <t>105418</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>134802</t>
+          <t>134161</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -10216,12 +10216,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>56,05%</t>
+          <t>55,69%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>71,21%</t>
+          <t>70,88%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -10236,12 +10236,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>215779</t>
+          <t>216610</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>254856</t>
+          <t>253296</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>56,35%</t>
+          <t>56,56%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>66,55%</t>
+          <t>66,14%</t>
         </is>
       </c>
     </row>
@@ -10279,12 +10279,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>28377</t>
+          <t>27633</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>50213</t>
+          <t>48675</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10294,12 +10294,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,27%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>25,13%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10314,12 +10314,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>23271</t>
+          <t>23784</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>45389</t>
+          <t>47625</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10329,12 +10329,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,56%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>23,98%</t>
+          <t>25,16%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10349,12 +10349,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>56746</t>
+          <t>56387</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>88299</t>
+          <t>88852</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10364,12 +10364,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>14,82%</t>
+          <t>14,72%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>23,2%</t>
         </is>
       </c>
     </row>
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1937</t>
+          <t>1989</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>11692</t>
+          <t>11216</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10407,12 +10407,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10427,12 +10427,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1442</t>
+          <t>1519</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>12427</t>
+          <t>12532</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10442,12 +10442,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>6,62%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10462,12 +10462,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4859</t>
+          <t>5175</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>18823</t>
+          <t>19244</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10477,12 +10477,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>1,27%</t>
+          <t>1,35%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,03%</t>
         </is>
       </c>
     </row>
@@ -10505,97 +10505,97 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K30" s="2" t="inlineStr">
+        <is>
+          <t>2529</t>
+        </is>
+      </c>
+      <c r="L30" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>1976</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
+      <c r="M30" s="2" t="inlineStr">
+        <is>
+          <t>8387</t>
+        </is>
+      </c>
+      <c r="N30" s="2" t="inlineStr">
+        <is>
+          <t>1,34%</t>
+        </is>
+      </c>
+      <c r="O30" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="inlineStr">
-        <is>
-          <t>1,02%</t>
-        </is>
-      </c>
-      <c r="J30" s="2" t="inlineStr">
+      <c r="P30" s="2" t="inlineStr">
+        <is>
+          <t>4,43%</t>
+        </is>
+      </c>
+      <c r="Q30" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K30" s="2" t="inlineStr">
+      <c r="R30" s="2" t="inlineStr">
         <is>
           <t>2529</t>
         </is>
       </c>
-      <c r="L30" s="2" t="inlineStr">
+      <c r="S30" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M30" s="2" t="inlineStr">
-        <is>
-          <t>8880</t>
-        </is>
-      </c>
-      <c r="N30" s="2" t="inlineStr">
-        <is>
-          <t>1,34%</t>
-        </is>
-      </c>
-      <c r="O30" s="2" t="inlineStr">
+      <c r="T30" s="2" t="inlineStr">
+        <is>
+          <t>9023</t>
+        </is>
+      </c>
+      <c r="U30" s="2" t="inlineStr">
+        <is>
+          <t>0,66%</t>
+        </is>
+      </c>
+      <c r="V30" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P30" s="2" t="inlineStr">
-        <is>
-          <t>4,69%</t>
-        </is>
-      </c>
-      <c r="Q30" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R30" s="2" t="inlineStr">
-        <is>
-          <t>2529</t>
-        </is>
-      </c>
-      <c r="S30" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T30" s="2" t="inlineStr">
-        <is>
-          <t>9068</t>
-        </is>
-      </c>
-      <c r="U30" s="2" t="inlineStr">
-        <is>
-          <t>0,66%</t>
-        </is>
-      </c>
-      <c r="V30" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -10771,7 +10771,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según el principal daño o lesión producido en el último accidente en 2023</t>
+          <t>Población según el principal daño o lesión producido en el último accidente en 2023 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -10966,12 +10966,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1953</t>
+          <t>1887</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9279</t>
+          <t>9659</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -10981,12 +10981,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>27,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -11001,12 +11001,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3775</t>
+          <t>3938</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12246</t>
+          <t>12414</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -11016,12 +11016,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>15,6%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11036,12 +11036,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7249</t>
+          <t>6914</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18670</t>
+          <t>18074</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -11051,12 +11051,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>6,0%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>15,69%</t>
         </is>
       </c>
     </row>
@@ -11084,7 +11084,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1920</t>
+          <t>1764</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -11099,7 +11099,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>5,39%</t>
+          <t>4,96%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11114,12 +11114,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1049</t>
+          <t>861</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7555</t>
+          <t>7571</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -11129,12 +11129,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,52%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11149,12 +11149,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1196</t>
+          <t>1291</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>7835</t>
+          <t>7657</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -11164,12 +11164,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,8%</t>
+          <t>6,65%</t>
         </is>
       </c>
     </row>
@@ -11192,12 +11192,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>15407</t>
+          <t>15072</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>25768</t>
+          <t>25804</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -11207,12 +11207,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>43,27%</t>
+          <t>42,33%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>72,37%</t>
+          <t>72,47%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11227,12 +11227,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>45294</t>
+          <t>44906</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>57566</t>
+          <t>57528</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -11242,12 +11242,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>56,93%</t>
+          <t>56,45%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>72,36%</t>
+          <t>72,31%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11262,12 +11262,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>63859</t>
+          <t>64187</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>80464</t>
+          <t>81481</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -11277,12 +11277,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>55,45%</t>
+          <t>55,74%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>69,87%</t>
+          <t>70,75%</t>
         </is>
       </c>
     </row>
@@ -11305,12 +11305,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5518</t>
+          <t>5543</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15589</t>
+          <t>15598</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -11320,12 +11320,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,57%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>43,78%</t>
+          <t>43,81%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11340,12 +11340,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11979</t>
+          <t>11835</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22248</t>
+          <t>22404</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -11355,12 +11355,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,97%</t>
+          <t>28,16%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11375,12 +11375,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>19345</t>
+          <t>19822</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>34390</t>
+          <t>34845</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -11390,12 +11390,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>29,86%</t>
+          <t>30,26%</t>
         </is>
       </c>
     </row>
@@ -11418,97 +11418,97 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>461</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>1261</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>2578</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>0,58%</t>
+        </is>
+      </c>
+      <c r="O8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>3,54%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
+      <c r="P8" s="2" t="inlineStr">
+        <is>
+          <t>3,24%</t>
+        </is>
+      </c>
+      <c r="Q8" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K8" s="2" t="inlineStr">
+      <c r="R8" s="2" t="inlineStr">
         <is>
           <t>461</t>
         </is>
       </c>
-      <c r="L8" s="2" t="inlineStr">
+      <c r="S8" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M8" s="2" t="inlineStr">
-        <is>
-          <t>3044</t>
-        </is>
-      </c>
-      <c r="N8" s="2" t="inlineStr">
-        <is>
-          <t>0,58%</t>
-        </is>
-      </c>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="T8" s="2" t="inlineStr">
+        <is>
+          <t>2474</t>
+        </is>
+      </c>
+      <c r="U8" s="2" t="inlineStr">
+        <is>
+          <t>0,4%</t>
+        </is>
+      </c>
+      <c r="V8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P8" s="2" t="inlineStr">
-        <is>
-          <t>3,83%</t>
-        </is>
-      </c>
-      <c r="Q8" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R8" s="2" t="inlineStr">
-        <is>
-          <t>461</t>
-        </is>
-      </c>
-      <c r="S8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" s="2" t="inlineStr">
-        <is>
-          <t>2375</t>
-        </is>
-      </c>
-      <c r="U8" s="2" t="inlineStr">
-        <is>
-          <t>0,4%</t>
-        </is>
-      </c>
-      <c r="V8" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,15%</t>
         </is>
       </c>
     </row>
@@ -11531,97 +11531,97 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>594</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>1261</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>2953</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>0,75%</t>
+        </is>
+      </c>
+      <c r="O9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>3,54%</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
+      <c r="P9" s="2" t="inlineStr">
+        <is>
+          <t>3,71%</t>
+        </is>
+      </c>
+      <c r="Q9" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K9" s="2" t="inlineStr">
+      <c r="R9" s="2" t="inlineStr">
         <is>
           <t>594</t>
         </is>
       </c>
-      <c r="L9" s="2" t="inlineStr">
+      <c r="S9" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M9" s="2" t="inlineStr">
-        <is>
-          <t>3279</t>
-        </is>
-      </c>
-      <c r="N9" s="2" t="inlineStr">
-        <is>
-          <t>0,75%</t>
-        </is>
-      </c>
-      <c r="O9" s="2" t="inlineStr">
+      <c r="T9" s="2" t="inlineStr">
+        <is>
+          <t>2900</t>
+        </is>
+      </c>
+      <c r="U9" s="2" t="inlineStr">
+        <is>
+          <t>0,52%</t>
+        </is>
+      </c>
+      <c r="V9" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P9" s="2" t="inlineStr">
-        <is>
-          <t>4,12%</t>
-        </is>
-      </c>
-      <c r="Q9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R9" s="2" t="inlineStr">
-        <is>
-          <t>594</t>
-        </is>
-      </c>
-      <c r="S9" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" s="2" t="inlineStr">
-        <is>
-          <t>2952</t>
-        </is>
-      </c>
-      <c r="U9" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
-      <c r="V9" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,52%</t>
         </is>
       </c>
     </row>
@@ -11761,12 +11761,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7154</t>
+          <t>7290</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>23159</t>
+          <t>24116</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -11776,12 +11776,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,61%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>17,81%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11796,12 +11796,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5235</t>
+          <t>5015</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14654</t>
+          <t>14292</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -11811,12 +11811,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>4,92%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>14,37%</t>
+          <t>14,02%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11831,12 +11831,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>14712</t>
+          <t>15295</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>34715</t>
+          <t>33556</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -11846,12 +11846,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>6,34%</t>
+          <t>6,59%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>14,96%</t>
+          <t>14,46%</t>
         </is>
       </c>
     </row>
@@ -11874,12 +11874,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9596</t>
+          <t>9737</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>33262</t>
+          <t>33070</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -11889,12 +11889,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,38%</t>
+          <t>7,49%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>25,58%</t>
+          <t>25,43%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11909,12 +11909,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2834</t>
+          <t>2770</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>19624</t>
+          <t>18213</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -11924,12 +11924,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>19,25%</t>
+          <t>17,86%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11944,12 +11944,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>15513</t>
+          <t>14172</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>44329</t>
+          <t>41908</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -11959,12 +11959,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,69%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>19,11%</t>
+          <t>18,06%</t>
         </is>
       </c>
     </row>
@@ -11987,12 +11987,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>48066</t>
+          <t>50093</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>76004</t>
+          <t>76680</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -12002,12 +12002,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>36,96%</t>
+          <t>38,52%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>58,45%</t>
+          <t>58,97%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12022,12 +12022,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>54305</t>
+          <t>54304</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>72936</t>
+          <t>73081</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -12042,7 +12042,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>71,54%</t>
+          <t>71,68%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12057,12 +12057,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>109781</t>
+          <t>111806</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>141273</t>
+          <t>143999</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -12072,12 +12072,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>47,32%</t>
+          <t>48,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>60,89%</t>
+          <t>62,07%</t>
         </is>
       </c>
     </row>
@@ -12100,12 +12100,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>23270</t>
+          <t>22573</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>44626</t>
+          <t>43466</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -12115,12 +12115,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>17,89%</t>
+          <t>17,36%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>34,32%</t>
+          <t>33,42%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12135,12 +12135,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>11942</t>
+          <t>12055</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>24868</t>
+          <t>25147</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -12150,12 +12150,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>24,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12170,12 +12170,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>38441</t>
+          <t>39672</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>60837</t>
+          <t>64953</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -12185,12 +12185,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>16,57%</t>
+          <t>17,1%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>26,22%</t>
+          <t>28,0%</t>
         </is>
       </c>
     </row>
@@ -12218,7 +12218,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4993</t>
+          <t>4697</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -12233,7 +12233,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -12248,12 +12248,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1315</t>
+          <t>1432</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>10907</t>
+          <t>11678</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -12263,12 +12263,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>11,45%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -12283,12 +12283,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2274</t>
+          <t>2050</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>11686</t>
+          <t>11756</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -12298,12 +12298,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,07%</t>
         </is>
       </c>
     </row>
@@ -12331,7 +12331,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7049</t>
+          <t>6741</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -12346,7 +12346,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,42%</t>
+          <t>5,18%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12361,62 +12361,62 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R16" s="2" t="inlineStr">
+        <is>
+          <t>1396</t>
+        </is>
+      </c>
+      <c r="S16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>1321</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>6471</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>0,6%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>1,3%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>1396</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>5801</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,6%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,79%</t>
         </is>
       </c>
     </row>
@@ -12556,12 +12556,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3069</t>
+          <t>2834</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>16834</t>
+          <t>18223</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -12571,12 +12571,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>9,24%</t>
+          <t>8,53%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>50,67%</t>
+          <t>54,85%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12591,12 +12591,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>579</t>
+          <t>594</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6283</t>
+          <t>6205</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -12606,12 +12606,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,1%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12626,12 +12626,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>4383</t>
+          <t>4866</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>21836</t>
+          <t>22293</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -12641,12 +12641,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,84%</t>
+          <t>7,59%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>34,78%</t>
         </is>
       </c>
     </row>
@@ -12674,7 +12674,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>8008</t>
+          <t>7509</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -12689,7 +12689,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>22,6%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12709,7 +12709,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>3183</t>
+          <t>4355</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -12724,7 +12724,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>10,31%</t>
+          <t>14,11%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12739,12 +12739,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>938</t>
+          <t>917</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8228</t>
+          <t>8638</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -12754,12 +12754,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>12,84%</t>
+          <t>13,48%</t>
         </is>
       </c>
     </row>
@@ -12782,12 +12782,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>8660</t>
+          <t>8543</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>22141</t>
+          <t>22578</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -12797,12 +12797,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>26,06%</t>
+          <t>25,71%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>66,64%</t>
+          <t>67,95%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12817,12 +12817,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>14617</t>
+          <t>14320</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>23204</t>
+          <t>22958</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -12832,12 +12832,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>47,36%</t>
+          <t>46,39%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>75,18%</t>
+          <t>74,38%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12852,12 +12852,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>25874</t>
+          <t>25954</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>42713</t>
+          <t>42377</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -12867,12 +12867,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>40,37%</t>
+          <t>40,49%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>66,64%</t>
+          <t>66,12%</t>
         </is>
       </c>
     </row>
@@ -12895,12 +12895,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2266</t>
+          <t>2377</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>10845</t>
+          <t>11320</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -12910,12 +12910,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>32,64%</t>
+          <t>34,07%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -12930,12 +12930,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>4278</t>
+          <t>4184</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>12154</t>
+          <t>11477</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -12945,12 +12945,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13,86%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>39,38%</t>
+          <t>37,18%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -12965,12 +12965,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>8174</t>
+          <t>8991</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>20582</t>
+          <t>20309</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -12980,12 +12980,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>14,03%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>32,11%</t>
+          <t>31,69%</t>
         </is>
       </c>
     </row>
@@ -13013,7 +13013,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4617</t>
+          <t>5267</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -13028,7 +13028,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>13,9%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13048,7 +13048,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>5067</t>
+          <t>3930</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -13063,7 +13063,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>12,73%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13083,7 +13083,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6046</t>
+          <t>6216</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -13098,7 +13098,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,43%</t>
+          <t>9,7%</t>
         </is>
       </c>
     </row>
@@ -13121,97 +13121,97 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>1865</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr">
+      <c r="K23" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N23" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="inlineStr">
-        <is>
-          <t>5,61%</t>
-        </is>
-      </c>
-      <c r="J23" s="2" t="inlineStr">
+      <c r="O23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P23" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q23" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K23" s="2" t="inlineStr">
+      <c r="R23" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M23" s="2" t="inlineStr">
-        <is>
-          <t>1093</t>
-        </is>
-      </c>
-      <c r="N23" s="2" t="inlineStr">
+      <c r="S23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T23" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U23" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O23" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P23" s="2" t="inlineStr">
-        <is>
-          <t>3,54%</t>
-        </is>
-      </c>
-      <c r="Q23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S23" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T23" s="2" t="inlineStr">
-        <is>
-          <t>1411</t>
-        </is>
-      </c>
-      <c r="U23" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -13351,12 +13351,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>17842</t>
+          <t>17288</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>42366</t>
+          <t>42334</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -13366,12 +13366,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,97%</t>
+          <t>8,69%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>21,3%</t>
+          <t>21,29%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13386,12 +13386,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>13247</t>
+          <t>12427</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>26819</t>
+          <t>26027</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -13401,12 +13401,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>6,24%</t>
+          <t>5,85%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,63%</t>
+          <t>12,26%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13421,12 +13421,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>33563</t>
+          <t>33515</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>63222</t>
+          <t>62309</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -13436,12 +13436,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>8,15%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,15%</t>
         </is>
       </c>
     </row>
@@ -13464,12 +13464,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>11291</t>
+          <t>11761</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>36740</t>
+          <t>36988</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -13479,12 +13479,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>5,68%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>18,47%</t>
+          <t>18,6%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13499,12 +13499,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>5690</t>
+          <t>6181</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>23280</t>
+          <t>23312</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -13514,12 +13514,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>10,98%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13534,12 +13534,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>20372</t>
+          <t>20269</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>51744</t>
+          <t>50046</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -13549,12 +13549,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,93%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>12,58%</t>
+          <t>12,17%</t>
         </is>
       </c>
     </row>
@@ -13577,12 +13577,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>83797</t>
+          <t>82063</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>115049</t>
+          <t>114575</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -13592,12 +13592,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>42,14%</t>
+          <t>41,26%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>57,85%</t>
+          <t>57,61%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -13612,12 +13612,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>120475</t>
+          <t>122937</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>146091</t>
+          <t>146270</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -13627,12 +13627,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>56,73%</t>
+          <t>57,89%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>68,79%</t>
+          <t>68,87%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -13647,12 +13647,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>213571</t>
+          <t>216145</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>252901</t>
+          <t>254803</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -13662,12 +13662,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>51,93%</t>
+          <t>52,56%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>61,5%</t>
+          <t>61,96%</t>
         </is>
       </c>
     </row>
@@ -13690,12 +13690,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>36377</t>
+          <t>36496</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>61173</t>
+          <t>61744</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -13705,12 +13705,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>18,29%</t>
+          <t>18,35%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>30,76%</t>
+          <t>31,05%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13725,12 +13725,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>33018</t>
+          <t>33559</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>51726</t>
+          <t>50988</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -13740,12 +13740,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15,55%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,01%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13760,12 +13760,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>75875</t>
+          <t>75392</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>105599</t>
+          <t>105818</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -13775,12 +13775,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>25,68%</t>
+          <t>25,73%</t>
         </is>
       </c>
     </row>
@@ -13808,7 +13808,7 @@
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>6830</t>
+          <t>7791</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -13823,7 +13823,7 @@
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13838,12 +13838,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2285</t>
+          <t>2259</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>12211</t>
+          <t>11397</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -13853,12 +13853,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,37%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13873,12 +13873,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>4088</t>
+          <t>3641</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>14403</t>
+          <t>14432</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -13888,12 +13888,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,51%</t>
         </is>
       </c>
     </row>
@@ -13921,7 +13921,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>5804</t>
+          <t>7229</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -13936,7 +13936,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -13956,7 +13956,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2969</t>
+          <t>2908</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -13971,7 +13971,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,37%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -13991,7 +13991,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>9062</t>
+          <t>7937</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -14006,7 +14006,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>1,93%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P15C-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P15C-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1036</t>
+          <t>1090</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8906</t>
+          <t>9347</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>4,12%</t>
+          <t>4,33%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>35,38%</t>
+          <t>37,13%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>4385</t>
+          <t>4414</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,63%</t>
+          <t>9,69%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>2016</t>
+          <t>2001</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11432</t>
+          <t>11521</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,83%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,17%</t>
+          <t>16,3%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>809</t>
+          <t>828</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7564</t>
+          <t>7666</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>30,05%</t>
+          <t>30,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1023</t>
+          <t>1017</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>8918</t>
+          <t>9360</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,25%</t>
+          <t>2,23%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>20,56%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2855</t>
+          <t>3004</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>13200</t>
+          <t>13582</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>18,67%</t>
+          <t>19,21%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>6694</t>
+          <t>7270</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>16841</t>
+          <t>17047</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>28,88%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>66,9%</t>
+          <t>67,71%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>24800</t>
+          <t>24394</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>37078</t>
+          <t>36900</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>54,47%</t>
+          <t>53,58%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>81,44%</t>
+          <t>81,05%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>34910</t>
+          <t>34715</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>51357</t>
+          <t>51657</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>49,38%</t>
+          <t>49,1%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>72,64%</t>
+          <t>73,06%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2538</t>
+          <t>2688</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>11145</t>
+          <t>12072</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>10,08%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>44,27%</t>
+          <t>47,95%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2729</t>
+          <t>3093</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>12942</t>
+          <t>12914</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,79%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,43%</t>
+          <t>28,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>7637</t>
+          <t>6987</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>20978</t>
+          <t>20285</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>10,8%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>29,67%</t>
+          <t>28,69%</t>
         </is>
       </c>
     </row>
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>834</t>
+          <t>828</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>7036</t>
+          <t>6315</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>13,87%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>827</t>
+          <t>832</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>6225</t>
+          <t>6884</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,17%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>9,74%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5834</t>
+          <t>5836</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>18593</t>
+          <t>17835</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>23,68%</t>
+          <t>22,72%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>908</t>
+          <t>891</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6959</t>
+          <t>6830</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>19,86%</t>
+          <t>19,49%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>8527</t>
+          <t>7726</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>22425</t>
+          <t>21088</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>6,8%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>18,57%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3390</t>
+          <t>3581</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15504</t>
+          <t>15543</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1656,12 +1656,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,56%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>19,75%</t>
+          <t>19,8%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1681,7 +1681,7 @@
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>4602</t>
+          <t>4181</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,13%</t>
+          <t>11,93%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>4253</t>
+          <t>4035</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>17047</t>
+          <t>16198</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,55%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>15,01%</t>
+          <t>14,27%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>25171</t>
+          <t>25828</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>42617</t>
+          <t>44067</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>32,06%</t>
+          <t>32,9%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>54,29%</t>
+          <t>56,13%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>15502</t>
+          <t>15998</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>27053</t>
+          <t>26932</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>44,24%</t>
+          <t>45,65%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>77,2%</t>
+          <t>76,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>44207</t>
+          <t>44589</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>66053</t>
+          <t>65618</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>38,93%</t>
+          <t>39,27%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>58,17%</t>
+          <t>57,79%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>11974</t>
+          <t>12038</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>27254</t>
+          <t>28494</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>34,72%</t>
+          <t>36,3%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3130</t>
+          <t>3142</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>13204</t>
+          <t>12792</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,97%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>37,68%</t>
+          <t>36,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>18603</t>
+          <t>18836</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>37427</t>
+          <t>37620</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>16,38%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>32,96%</t>
+          <t>33,13%</t>
         </is>
       </c>
     </row>
@@ -1980,12 +1980,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>2871</t>
+          <t>2876</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>12808</t>
+          <t>12973</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -2000,7 +2000,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,53%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2020,7 +2020,7 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>6255</t>
+          <t>7054</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>17,85%</t>
+          <t>20,13%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2050,12 +2050,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>4611</t>
+          <t>3896</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>15532</t>
+          <t>15473</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2065,12 +2065,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>13,63%</t>
         </is>
       </c>
     </row>
@@ -2363,7 +2363,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5515</t>
+          <t>6136</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2378,7 +2378,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>41,66%</t>
+          <t>46,36%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2398,7 +2398,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>5948</t>
+          <t>6883</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2413,7 +2413,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>21,76%</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2441,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>5873</t>
+          <t>5790</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>31,47%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2511,7 +2511,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6344</t>
+          <t>5172</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,06%</t>
+          <t>16,35%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>8642</t>
+          <t>8689</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>17236</t>
+          <t>16740</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>46,98%</t>
+          <t>47,23%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>93,69%</t>
+          <t>90,99%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>3700</t>
+          <t>3880</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>11239</t>
+          <t>11184</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>29,31%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>84,91%</t>
+          <t>84,5%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>14911</t>
+          <t>14210</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>25838</t>
+          <t>26182</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>47,14%</t>
+          <t>44,92%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>81,68%</t>
+          <t>82,77%</t>
         </is>
       </c>
     </row>
@@ -2667,7 +2667,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>8171</t>
+          <t>7101</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2682,7 +2682,7 @@
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>44,41%</t>
+          <t>38,6%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2697,12 +2697,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>962</t>
+          <t>1008</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>7864</t>
+          <t>7833</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2712,12 +2712,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>7,26%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>59,41%</t>
+          <t>59,18%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2732,12 +2732,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1586</t>
+          <t>1759</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>11882</t>
+          <t>11933</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2747,12 +2747,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>37,56%</t>
+          <t>37,72%</t>
         </is>
       </c>
     </row>
@@ -2780,7 +2780,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>3977</t>
+          <t>5226</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2795,7 +2795,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>28,41%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2850,7 +2850,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4680</t>
+          <t>6533</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2865,7 +2865,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>14,79%</t>
+          <t>20,65%</t>
         </is>
       </c>
     </row>
@@ -2893,7 +2893,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>4586</t>
+          <t>5266</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2908,7 +2908,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>28,62%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2963,7 +2963,7 @@
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>8071</t>
+          <t>5368</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2978,7 +2978,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>25,51%</t>
+          <t>16,97%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>9081</t>
+          <t>8914</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>23218</t>
+          <t>22600</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>7,44%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>19,02%</t>
+          <t>18,51%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2002</t>
+          <t>2777</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>12789</t>
+          <t>12075</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>12,87%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>13336</t>
+          <t>13318</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>31008</t>
+          <t>31053</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>6,18%</t>
+          <t>6,17%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>14,36%</t>
+          <t>14,38%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>6730</t>
+          <t>6250</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>21069</t>
+          <t>21111</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,12%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>1090</t>
+          <t>1154</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>10346</t>
+          <t>10637</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>11,03%</t>
+          <t>11,34%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>9727</t>
+          <t>9887</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>24545</t>
+          <t>26346</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>12,2%</t>
         </is>
       </c>
     </row>
@@ -3344,12 +3344,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>48247</t>
+          <t>48910</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>71006</t>
+          <t>70576</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -3359,12 +3359,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>39,52%</t>
+          <t>40,07%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>58,17%</t>
+          <t>57,81%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -3379,12 +3379,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>51596</t>
+          <t>51136</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>70832</t>
+          <t>69584</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -3394,12 +3394,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>55,0%</t>
+          <t>54,51%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>75,51%</t>
+          <t>74,18%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -3414,12 +3414,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>104205</t>
+          <t>104432</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>133501</t>
+          <t>133492</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -3429,7 +3429,7 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>48,27%</t>
+          <t>48,38%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
@@ -3457,12 +3457,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>19376</t>
+          <t>18388</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>37915</t>
+          <t>38028</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -3472,12 +3472,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>15,06%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>31,06%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -3492,12 +3492,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>11096</t>
+          <t>11269</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>27007</t>
+          <t>25809</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -3507,12 +3507,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11,83%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>28,79%</t>
+          <t>27,51%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -3527,12 +3527,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>33184</t>
+          <t>33810</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>58240</t>
+          <t>57730</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -3542,12 +3542,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>15,37%</t>
+          <t>15,66%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>26,98%</t>
+          <t>26,74%</t>
         </is>
       </c>
     </row>
@@ -3570,12 +3570,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>3738</t>
+          <t>3527</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>13687</t>
+          <t>13876</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -3585,12 +3585,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,37%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -3605,12 +3605,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1709</t>
+          <t>1840</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>10156</t>
+          <t>10555</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -3620,12 +3620,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>10,83%</t>
+          <t>11,25%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -3640,12 +3640,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>6603</t>
+          <t>6564</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>19526</t>
+          <t>20202</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -3655,12 +3655,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>3,06%</t>
+          <t>3,04%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>9,04%</t>
+          <t>9,36%</t>
         </is>
       </c>
     </row>
@@ -3688,7 +3688,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>6171</t>
+          <t>5691</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -3703,7 +3703,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>5,05%</t>
+          <t>4,66%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -3758,7 +3758,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>6038</t>
+          <t>5237</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -3773,7 +3773,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,43%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1078</t>
+          <t>1067</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10323</t>
+          <t>9895</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>13,63%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>2050</t>
+          <t>2104</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12051</t>
+          <t>11823</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4381</t>
+          <t>4455</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17377</t>
+          <t>17175</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,32%</t>
+          <t>2,36%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,21%</t>
+          <t>9,1%</t>
         </is>
       </c>
     </row>
@@ -4257,12 +4257,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1458</t>
+          <t>1735</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>9255</t>
+          <t>9935</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4272,12 +4272,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,22%</t>
+          <t>13,11%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4292,12 +4292,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2914</t>
+          <t>2079</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12176</t>
+          <t>12762</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4307,12 +4307,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>1,84%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,78%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4327,12 +4327,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>5651</t>
+          <t>5633</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>17716</t>
+          <t>17916</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4347,7 +4347,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,39%</t>
+          <t>9,49%</t>
         </is>
       </c>
     </row>
@@ -4370,12 +4370,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>35171</t>
+          <t>36267</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>53632</t>
+          <t>54023</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -4385,12 +4385,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>46,43%</t>
+          <t>47,87%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>70,8%</t>
+          <t>71,31%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -4405,12 +4405,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>51197</t>
+          <t>50304</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>72419</t>
+          <t>73056</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -4420,12 +4420,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>45,33%</t>
+          <t>44,54%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>64,12%</t>
+          <t>64,69%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -4440,12 +4440,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>93517</t>
+          <t>94809</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>121536</t>
+          <t>122107</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4455,12 +4455,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>49,56%</t>
+          <t>50,25%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>64,41%</t>
+          <t>64,71%</t>
         </is>
       </c>
     </row>
@@ -4483,12 +4483,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>8367</t>
+          <t>8655</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>23185</t>
+          <t>22930</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4498,12 +4498,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>11,04%</t>
+          <t>11,42%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>30,27%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4518,12 +4518,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11498</t>
+          <t>11455</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>27384</t>
+          <t>27448</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4533,12 +4533,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,18%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>24,25%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4553,12 +4553,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>22876</t>
+          <t>22731</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>44636</t>
+          <t>42750</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4568,12 +4568,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>22,66%</t>
         </is>
       </c>
     </row>
@@ -4596,12 +4596,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>3281</t>
+          <t>3016</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>14578</t>
+          <t>15454</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4611,12 +4611,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>4,33%</t>
+          <t>3,98%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>19,24%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4631,12 +4631,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>13816</t>
+          <t>13773</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>30624</t>
+          <t>31874</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4646,12 +4646,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12,23%</t>
+          <t>12,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>28,22%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4666,12 +4666,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>20193</t>
+          <t>19208</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>39938</t>
+          <t>39869</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,18%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>21,17%</t>
+          <t>21,13%</t>
         </is>
       </c>
     </row>
@@ -4939,12 +4939,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>5511</t>
+          <t>5519</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>19019</t>
+          <t>19427</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4959,7 +4959,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,71%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4974,12 +4974,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4952</t>
+          <t>4763</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>17679</t>
+          <t>16627</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4989,12 +4989,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,32%</t>
+          <t>4,15%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>14,49%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -5009,12 +5009,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>13134</t>
+          <t>13679</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>30890</t>
+          <t>31458</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -5024,12 +5024,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>10,43%</t>
+          <t>10,62%</t>
         </is>
       </c>
     </row>
@@ -5052,12 +5052,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8383</t>
+          <t>8544</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>24358</t>
+          <t>24652</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -5067,12 +5067,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,42%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -5087,12 +5087,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4261</t>
+          <t>4874</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>16670</t>
+          <t>16557</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -5102,12 +5102,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>14,53%</t>
+          <t>14,43%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -5122,12 +5122,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>16277</t>
+          <t>16195</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>36343</t>
+          <t>36016</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -5137,12 +5137,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>5,5%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>12,27%</t>
+          <t>12,16%</t>
         </is>
       </c>
     </row>
@@ -5165,12 +5165,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>106891</t>
+          <t>107751</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>132479</t>
+          <t>133055</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -5180,12 +5180,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>58,91%</t>
+          <t>59,38%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>73,01%</t>
+          <t>73,33%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5200,12 +5200,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>49348</t>
+          <t>48623</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>70198</t>
+          <t>70247</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5215,12 +5215,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>43,02%</t>
+          <t>42,39%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>61,19%</t>
+          <t>61,24%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5235,12 +5235,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>163421</t>
+          <t>164627</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>198124</t>
+          <t>197603</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5250,12 +5250,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>55,18%</t>
+          <t>55,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>66,89%</t>
+          <t>66,72%</t>
         </is>
       </c>
     </row>
@@ -5278,12 +5278,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>14489</t>
+          <t>14633</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>34058</t>
+          <t>34876</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5293,12 +5293,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>7,98%</t>
+          <t>8,06%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>18,77%</t>
+          <t>19,22%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5313,12 +5313,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>11447</t>
+          <t>12010</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>27755</t>
+          <t>27347</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5328,12 +5328,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>9,98%</t>
+          <t>10,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>24,19%</t>
+          <t>23,84%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5348,12 +5348,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>29638</t>
+          <t>30769</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>54512</t>
+          <t>54657</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5363,12 +5363,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>18,41%</t>
+          <t>18,45%</t>
         </is>
       </c>
     </row>
@@ -5391,12 +5391,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>5235</t>
+          <t>5159</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>17636</t>
+          <t>17935</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -5406,12 +5406,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2,88%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,88%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -5426,12 +5426,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>9642</t>
+          <t>10376</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>25413</t>
+          <t>27017</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>23,55%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>17802</t>
+          <t>17106</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>39206</t>
+          <t>38153</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>13,24%</t>
+          <t>12,88%</t>
         </is>
       </c>
     </row>
@@ -5509,7 +5509,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>4779</t>
+          <t>4421</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5524,7 +5524,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5579,7 +5579,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>5741</t>
+          <t>5140</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5594,7 +5594,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,74%</t>
         </is>
       </c>
     </row>
@@ -5739,7 +5739,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>4885</t>
+          <t>4860</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5754,7 +5754,7 @@
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>18,75%</t>
+          <t>18,66%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5774,7 +5774,7 @@
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>8255</t>
+          <t>8358</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5789,7 +5789,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5809,7 +5809,7 @@
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>10058</t>
+          <t>9634</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5824,7 +5824,7 @@
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>18,7%</t>
+          <t>17,91%</t>
         </is>
       </c>
     </row>
@@ -5852,7 +5852,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>4208</t>
+          <t>5194</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5867,7 +5867,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>16,15%</t>
+          <t>19,94%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5887,7 +5887,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>5665</t>
+          <t>5199</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5902,7 +5902,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>20,43%</t>
+          <t>18,75%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5922,7 +5922,7 @@
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>6298</t>
+          <t>6680</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5937,7 +5937,7 @@
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>12,42%</t>
         </is>
       </c>
     </row>
@@ -5960,12 +5960,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>16647</t>
+          <t>15791</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>24213</t>
+          <t>24105</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5975,12 +5975,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>63,89%</t>
+          <t>60,61%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>92,93%</t>
+          <t>92,52%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5995,12 +5995,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>12323</t>
+          <t>12542</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>23458</t>
+          <t>23522</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -6010,12 +6010,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>44,44%</t>
+          <t>45,23%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>84,59%</t>
+          <t>84,82%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -6030,12 +6030,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>32462</t>
+          <t>31817</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>45619</t>
+          <t>46069</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -6045,12 +6045,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>60,36%</t>
+          <t>59,16%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>84,82%</t>
+          <t>85,65%</t>
         </is>
       </c>
     </row>
@@ -6073,12 +6073,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>887</t>
+          <t>903</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>7106</t>
+          <t>7633</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -6088,12 +6088,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>29,3%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -6113,7 +6113,7 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>6397</t>
+          <t>7255</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -6128,7 +6128,7 @@
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>23,07%</t>
+          <t>26,16%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -6143,12 +6143,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>978</t>
+          <t>1188</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>10400</t>
+          <t>9647</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -6158,12 +6158,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>2,21%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>19,34%</t>
+          <t>17,94%</t>
         </is>
       </c>
     </row>
@@ -6221,12 +6221,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1051</t>
+          <t>1044</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>10539</t>
+          <t>10162</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -6236,12 +6236,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>38,0%</t>
+          <t>36,65%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -6256,12 +6256,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1010</t>
+          <t>1034</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>12457</t>
+          <t>11407</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -6271,12 +6271,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>23,16%</t>
+          <t>21,21%</t>
         </is>
       </c>
     </row>
@@ -6529,12 +6529,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>9596</t>
+          <t>8885</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>26888</t>
+          <t>24407</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6544,12 +6544,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>3,39%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>8,62%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6564,12 +6564,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>10097</t>
+          <t>10765</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>26521</t>
+          <t>27448</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6579,12 +6579,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>4,22%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>10,38%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6599,12 +6599,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>23840</t>
+          <t>23451</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>46343</t>
+          <t>45800</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6614,12 +6614,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,5%</t>
         </is>
       </c>
     </row>
@@ -6642,12 +6642,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>13318</t>
+          <t>13150</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>30970</t>
+          <t>30819</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6657,12 +6657,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>4,7%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>10,88%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6677,12 +6677,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>10076</t>
+          <t>9297</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>25065</t>
+          <t>25086</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6692,12 +6692,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>3,95%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>9,81%</t>
+          <t>9,82%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6712,12 +6712,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>25889</t>
+          <t>26673</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>49836</t>
+          <t>51173</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6727,12 +6727,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>4,81%</t>
+          <t>4,95%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,5%</t>
         </is>
       </c>
     </row>
@@ -6755,12 +6755,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>170334</t>
+          <t>171155</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>204292</t>
+          <t>203881</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -6770,12 +6770,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>60,13%</t>
+          <t>60,42%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>72,12%</t>
+          <t>71,98%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -6790,12 +6790,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>123343</t>
+          <t>125507</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>157410</t>
+          <t>157415</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -6805,7 +6805,7 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>48,3%</t>
+          <t>49,14%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
@@ -6825,12 +6825,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>305430</t>
+          <t>304363</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>352370</t>
+          <t>349367</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>56,7%</t>
+          <t>56,5%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>65,42%</t>
+          <t>64,86%</t>
         </is>
       </c>
     </row>
@@ -6868,12 +6868,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>29346</t>
+          <t>29631</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>53193</t>
+          <t>54646</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -6883,12 +6883,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>10,36%</t>
+          <t>10,46%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>19,29%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>28093</t>
+          <t>28119</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>51215</t>
+          <t>50402</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -6918,12 +6918,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>11,0%</t>
+          <t>11,01%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>20,05%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -6938,12 +6938,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>62737</t>
+          <t>61752</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>96960</t>
+          <t>96908</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -6953,12 +6953,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>11,65%</t>
+          <t>11,46%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>18,0%</t>
+          <t>17,99%</t>
         </is>
       </c>
     </row>
@@ -6981,12 +6981,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>10384</t>
+          <t>10743</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>27421</t>
+          <t>27395</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -6996,12 +6996,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>3,79%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>9,68%</t>
+          <t>9,67%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -7016,12 +7016,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>29599</t>
+          <t>30700</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>54510</t>
+          <t>55049</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -7031,12 +7031,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>11,59%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>21,34%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -7051,12 +7051,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>46438</t>
+          <t>46661</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>77053</t>
+          <t>76377</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -7066,12 +7066,12 @@
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>14,3%</t>
+          <t>14,18%</t>
         </is>
       </c>
     </row>
@@ -7099,7 +7099,7 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>5081</t>
+          <t>5330</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
@@ -7114,7 +7114,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>1,79%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -7169,7 +7169,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>4800</t>
+          <t>5024</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -7184,7 +7184,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,93%</t>
         </is>
       </c>
     </row>
@@ -7555,12 +7555,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>940</t>
+          <t>984</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8531</t>
+          <t>8545</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -7570,12 +7570,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>2,09%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,0%</t>
+          <t>19,03%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -7595,7 +7595,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6557</t>
+          <t>6456</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -7610,7 +7610,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,05%</t>
+          <t>8,91%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -7625,12 +7625,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1803</t>
+          <t>1829</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10823</t>
+          <t>10870</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -7640,12 +7640,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>9,22%</t>
+          <t>9,26%</t>
         </is>
       </c>
     </row>
@@ -7668,12 +7668,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>2012</t>
+          <t>2652</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10818</t>
+          <t>11614</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -7683,12 +7683,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,48%</t>
+          <t>5,91%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>25,87%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -7703,12 +7703,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>2316</t>
+          <t>2946</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>12874</t>
+          <t>13632</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -7718,12 +7718,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>4,07%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,77%</t>
+          <t>18,82%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -7738,12 +7738,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>6851</t>
+          <t>6256</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>19740</t>
+          <t>19916</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -7753,12 +7753,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>5,84%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>16,97%</t>
         </is>
       </c>
     </row>
@@ -7781,12 +7781,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>17689</t>
+          <t>17722</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>29683</t>
+          <t>30145</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -7796,12 +7796,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>39,4%</t>
+          <t>39,47%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>66,11%</t>
+          <t>67,14%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -7816,12 +7816,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>39966</t>
+          <t>39900</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>57263</t>
+          <t>57671</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -7831,12 +7831,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>55,17%</t>
+          <t>55,08%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>79,05%</t>
+          <t>79,61%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -7851,12 +7851,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>62137</t>
+          <t>62894</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>83685</t>
+          <t>84768</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -7866,12 +7866,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>52,96%</t>
+          <t>53,6%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>71,32%</t>
+          <t>72,24%</t>
         </is>
       </c>
     </row>
@@ -7894,12 +7894,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5497</t>
+          <t>5674</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>16469</t>
+          <t>16591</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7909,12 +7909,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,64%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>36,68%</t>
+          <t>36,95%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7929,12 +7929,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>7918</t>
+          <t>8310</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>23862</t>
+          <t>23739</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7944,12 +7944,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>10,93%</t>
+          <t>11,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>32,94%</t>
+          <t>32,77%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7964,12 +7964,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>16728</t>
+          <t>17180</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>35876</t>
+          <t>35489</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7979,12 +7979,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>14,26%</t>
+          <t>14,64%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>30,25%</t>
         </is>
       </c>
     </row>
@@ -8012,7 +8012,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5569</t>
+          <t>4913</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8027,7 +8027,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8082,7 +8082,7 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>5392</t>
+          <t>5472</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8097,7 +8097,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,66%</t>
         </is>
       </c>
     </row>
@@ -8350,12 +8350,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>4506</t>
+          <t>4502</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>17349</t>
+          <t>17082</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -8370,7 +8370,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,71%</t>
+          <t>14,48%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -8385,12 +8385,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5095</t>
+          <t>5011</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>17581</t>
+          <t>18215</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -8400,12 +8400,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>5,84%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>21,22%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -8420,12 +8420,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>11386</t>
+          <t>11023</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>29821</t>
+          <t>28685</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -8435,12 +8435,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>5,59%</t>
+          <t>5,41%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>14,63%</t>
+          <t>14,07%</t>
         </is>
       </c>
     </row>
@@ -8463,12 +8463,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3468</t>
+          <t>3746</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15849</t>
+          <t>16032</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -8478,12 +8478,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,94%</t>
+          <t>3,18%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>13,44%</t>
+          <t>13,59%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -8498,12 +8498,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2897</t>
+          <t>2805</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>11645</t>
+          <t>13341</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -8513,12 +8513,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>15,54%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -8533,12 +8533,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>8374</t>
+          <t>8043</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>23429</t>
+          <t>24309</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -8548,12 +8548,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>3,95%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,5%</t>
+          <t>11,93%</t>
         </is>
       </c>
     </row>
@@ -8576,12 +8576,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>64636</t>
+          <t>64047</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>86092</t>
+          <t>86101</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -8591,12 +8591,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>54,79%</t>
+          <t>54,29%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>72,98%</t>
+          <t>72,99%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -8611,12 +8611,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>40192</t>
+          <t>40705</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>59059</t>
+          <t>59589</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -8626,12 +8626,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>46,82%</t>
+          <t>47,42%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>68,8%</t>
+          <t>69,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -8646,12 +8646,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>112802</t>
+          <t>109694</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>140438</t>
+          <t>138577</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -8661,12 +8661,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>55,35%</t>
+          <t>53,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>68,91%</t>
+          <t>67,99%</t>
         </is>
       </c>
     </row>
@@ -8689,12 +8689,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>13123</t>
+          <t>13303</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>30616</t>
+          <t>30530</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -8704,12 +8704,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>11,12%</t>
+          <t>11,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>25,88%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -8724,12 +8724,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>6373</t>
+          <t>6992</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>20642</t>
+          <t>19602</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -8739,12 +8739,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,42%</t>
+          <t>8,14%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>24,05%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -8759,12 +8759,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>23564</t>
+          <t>23991</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>45416</t>
+          <t>46190</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -8774,12 +8774,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,77%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>22,66%</t>
         </is>
       </c>
     </row>
@@ -8802,12 +8802,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>1042</t>
+          <t>1020</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>9347</t>
+          <t>9248</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -8817,12 +8817,12 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -8837,12 +8837,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1198</t>
+          <t>1180</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>11237</t>
+          <t>11219</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -8852,12 +8852,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>13,09%</t>
+          <t>13,07%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -8872,12 +8872,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>4037</t>
+          <t>3880</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>17442</t>
+          <t>16367</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -8887,12 +8887,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>8,56%</t>
+          <t>8,03%</t>
         </is>
       </c>
     </row>
@@ -8955,7 +8955,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>7807</t>
+          <t>7495</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8970,7 +8970,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>9,09%</t>
+          <t>8,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8990,7 +8990,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>9330</t>
+          <t>8494</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9005,7 +9005,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,17%</t>
         </is>
       </c>
     </row>
@@ -9145,12 +9145,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1916</t>
+          <t>1862</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>11768</t>
+          <t>11222</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9160,39 +9160,39 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
+          <t>6,05%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>36,44%</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>1929</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>6275</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
           <t>6,22%</t>
         </is>
       </c>
-      <c r="I18" s="2" t="inlineStr">
-        <is>
-          <t>38,21%</t>
-        </is>
-      </c>
-      <c r="J18" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K18" s="2" t="inlineStr">
-        <is>
-          <t>1929</t>
-        </is>
-      </c>
-      <c r="L18" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M18" s="2" t="inlineStr">
-        <is>
-          <t>6318</t>
-        </is>
-      </c>
-      <c r="N18" s="2" t="inlineStr">
-        <is>
-          <t>6,22%</t>
-        </is>
-      </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
@@ -9200,7 +9200,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20,37%</t>
+          <t>20,24%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9215,12 +9215,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3003</t>
+          <t>3106</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>13978</t>
+          <t>14266</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9230,12 +9230,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>5,02%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>22,62%</t>
+          <t>23,08%</t>
         </is>
       </c>
     </row>
@@ -9263,7 +9263,7 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>6606</t>
+          <t>6339</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -9298,7 +9298,7 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>8209</t>
+          <t>7732</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -9313,7 +9313,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>26,48%</t>
+          <t>24,93%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -9328,12 +9328,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>1042</t>
+          <t>1082</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>10244</t>
+          <t>10230</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -9343,12 +9343,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,75%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>16,58%</t>
+          <t>16,55%</t>
         </is>
       </c>
     </row>
@@ -9371,12 +9371,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>10077</t>
+          <t>10200</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>21553</t>
+          <t>22039</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -9386,12 +9386,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>69,99%</t>
+          <t>71,56%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -9406,12 +9406,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>13881</t>
+          <t>13829</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>25463</t>
+          <t>25664</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -9421,12 +9421,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>44,77%</t>
+          <t>44,6%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>82,12%</t>
+          <t>82,77%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -9441,12 +9441,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>27047</t>
+          <t>27751</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>44414</t>
+          <t>44339</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -9456,12 +9456,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>43,76%</t>
+          <t>44,9%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>71,86%</t>
+          <t>71,74%</t>
         </is>
       </c>
     </row>
@@ -9484,12 +9484,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2388</t>
+          <t>2290</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>12478</t>
+          <t>13262</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -9499,12 +9499,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>7,44%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>40,52%</t>
+          <t>43,06%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -9519,12 +9519,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2191</t>
+          <t>2074</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>13343</t>
+          <t>12954</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -9534,12 +9534,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>43,03%</t>
+          <t>41,78%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -9554,12 +9554,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>6847</t>
+          <t>6762</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>22797</t>
+          <t>21488</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -9569,12 +9569,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>10,94%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>36,89%</t>
+          <t>34,77%</t>
         </is>
       </c>
     </row>
@@ -9602,7 +9602,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>4842</t>
+          <t>4355</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -9617,7 +9617,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -9672,7 +9672,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4613</t>
+          <t>4394</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -9687,7 +9687,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,11%</t>
         </is>
       </c>
     </row>
@@ -9940,12 +9940,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>11049</t>
+          <t>10752</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>27999</t>
+          <t>27969</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9955,12 +9955,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,44%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9975,12 +9975,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>7001</t>
+          <t>7499</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>21579</t>
+          <t>21226</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9990,12 +9990,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -10010,12 +10010,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>21878</t>
+          <t>20643</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>43522</t>
+          <t>43508</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -10025,7 +10025,7 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>5,71%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
@@ -10053,12 +10053,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>9210</t>
+          <t>9205</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>25467</t>
+          <t>24825</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -10068,49 +10068,49 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>4,75%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
+          <t>12,82%</t>
+        </is>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="K26" s="2" t="inlineStr">
+        <is>
+          <t>14928</t>
+        </is>
+      </c>
+      <c r="L26" s="2" t="inlineStr">
+        <is>
+          <t>8851</t>
+        </is>
+      </c>
+      <c r="M26" s="2" t="inlineStr">
+        <is>
+          <t>24883</t>
+        </is>
+      </c>
+      <c r="N26" s="2" t="inlineStr">
+        <is>
+          <t>7,89%</t>
+        </is>
+      </c>
+      <c r="O26" s="2" t="inlineStr">
+        <is>
+          <t>4,68%</t>
+        </is>
+      </c>
+      <c r="P26" s="2" t="inlineStr">
+        <is>
           <t>13,15%</t>
         </is>
       </c>
-      <c r="J26" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="K26" s="2" t="inlineStr">
-        <is>
-          <t>14928</t>
-        </is>
-      </c>
-      <c r="L26" s="2" t="inlineStr">
-        <is>
-          <t>8542</t>
-        </is>
-      </c>
-      <c r="M26" s="2" t="inlineStr">
-        <is>
-          <t>25203</t>
-        </is>
-      </c>
-      <c r="N26" s="2" t="inlineStr">
-        <is>
-          <t>7,89%</t>
-        </is>
-      </c>
-      <c r="O26" s="2" t="inlineStr">
-        <is>
-          <t>4,51%</t>
-        </is>
-      </c>
-      <c r="P26" s="2" t="inlineStr">
-        <is>
-          <t>13,31%</t>
-        </is>
-      </c>
       <c r="Q26" s="2" t="inlineStr">
         <is>
           <t>29</t>
@@ -10123,12 +10123,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>21815</t>
+          <t>21279</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>44356</t>
+          <t>42218</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -10138,12 +10138,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>5,7%</t>
+          <t>5,56%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,02%</t>
         </is>
       </c>
     </row>
@@ -10166,12 +10166,12 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>101895</t>
+          <t>101199</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>129307</t>
+          <t>129122</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -10181,12 +10181,12 @@
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>52,62%</t>
+          <t>52,26%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>66,77%</t>
+          <t>66,67%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -10201,12 +10201,12 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>105418</t>
+          <t>105724</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>134161</t>
+          <t>132937</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -10216,12 +10216,12 @@
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>55,69%</t>
+          <t>55,85%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>70,88%</t>
+          <t>70,23%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -10236,12 +10236,12 @@
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>216610</t>
+          <t>216209</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>253296</t>
+          <t>254582</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
@@ -10251,12 +10251,12 @@
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>56,56%</t>
+          <t>56,46%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>66,14%</t>
+          <t>66,48%</t>
         </is>
       </c>
     </row>
@@ -10279,12 +10279,12 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>27633</t>
+          <t>27615</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>48675</t>
+          <t>50903</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
@@ -10294,12 +10294,12 @@
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>14,27%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>26,28%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -10314,12 +10314,12 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>23784</t>
+          <t>24183</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>47625</t>
+          <t>46463</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
@@ -10329,12 +10329,12 @@
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,78%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -10349,12 +10349,12 @@
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>56387</t>
+          <t>55367</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>88852</t>
+          <t>89625</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
@@ -10364,12 +10364,12 @@
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>14,72%</t>
+          <t>14,46%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>23,2%</t>
+          <t>23,4%</t>
         </is>
       </c>
     </row>
@@ -10392,12 +10392,12 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>1989</t>
+          <t>2099</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>11216</t>
+          <t>12729</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
@@ -10407,12 +10407,12 @@
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>5,79%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -10427,12 +10427,12 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>1519</t>
+          <t>1193</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>12532</t>
+          <t>11009</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
@@ -10442,12 +10442,12 @@
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>0,8%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>6,62%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -10462,12 +10462,12 @@
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>5175</t>
+          <t>5173</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>19244</t>
+          <t>19085</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
@@ -10482,7 +10482,7 @@
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>4,98%</t>
         </is>
       </c>
     </row>
@@ -10545,7 +10545,7 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>8387</t>
+          <t>9254</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
@@ -10560,7 +10560,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -10580,7 +10580,7 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>9023</t>
+          <t>8513</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
@@ -10595,7 +10595,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,22%</t>
         </is>
       </c>
     </row>
@@ -10961,32 +10961,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>4830</t>
+          <t>5332</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1887</t>
+          <t>1991</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>9659</t>
+          <t>10758</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>13,57%</t>
+          <t>14,09%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,26%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>27,13%</t>
+          <t>28,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -10996,32 +10996,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>7112</t>
+          <t>7732</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3938</t>
+          <t>4143</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12414</t>
+          <t>12559</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -11031,32 +11031,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>11942</t>
+          <t>13064</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6914</t>
+          <t>8025</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18074</t>
+          <t>19321</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>6,0%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,69%</t>
+          <t>15,79%</t>
         </is>
       </c>
     </row>
@@ -11074,7 +11074,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>346</t>
+          <t>345</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -11084,12 +11084,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1764</t>
+          <t>2009</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -11099,7 +11099,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,96%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -11109,32 +11109,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2951</t>
+          <t>3237</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>861</t>
+          <t>1179</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7571</t>
+          <t>8946</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>10,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -11144,32 +11144,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>3297</t>
+          <t>3581</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1291</t>
+          <t>1314</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>7657</t>
+          <t>8664</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>7,08%</t>
         </is>
       </c>
     </row>
@@ -11187,32 +11187,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>20729</t>
+          <t>21916</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>15072</t>
+          <t>16648</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>25804</t>
+          <t>27715</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>58,22%</t>
+          <t>57,91%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>42,33%</t>
+          <t>43,99%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>72,47%</t>
+          <t>73,24%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -11222,32 +11222,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>51911</t>
+          <t>54024</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>44906</t>
+          <t>46940</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>57528</t>
+          <t>59985</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>65,25%</t>
+          <t>63,92%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>56,45%</t>
+          <t>55,54%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>72,31%</t>
+          <t>70,97%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -11257,32 +11257,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>72640</t>
+          <t>75941</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>64187</t>
+          <t>67238</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>81481</t>
+          <t>84436</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>63,08%</t>
+          <t>62,06%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>55,74%</t>
+          <t>54,95%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>70,75%</t>
+          <t>69,0%</t>
         </is>
       </c>
     </row>
@@ -11300,32 +11300,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>9700</t>
+          <t>10250</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>5543</t>
+          <t>5525</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>15598</t>
+          <t>15925</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>27,24%</t>
+          <t>27,08%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>43,81%</t>
+          <t>42,08%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -11335,32 +11335,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>16525</t>
+          <t>18411</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>11835</t>
+          <t>13418</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>22404</t>
+          <t>24538</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>20,77%</t>
+          <t>21,78%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,88%</t>
+          <t>15,88%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>29,03%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -11370,32 +11370,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>26226</t>
+          <t>28660</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>19822</t>
+          <t>20911</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>34845</t>
+          <t>36679</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>22,77%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,21%</t>
+          <t>17,09%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,26%</t>
+          <t>29,98%</t>
         </is>
       </c>
     </row>
@@ -11448,7 +11448,7 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>509</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
@@ -11458,12 +11458,12 @@
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>2578</t>
+          <t>2659</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
@@ -11473,7 +11473,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,15%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -11483,7 +11483,7 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>461</t>
+          <t>509</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
@@ -11493,12 +11493,12 @@
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>2474</t>
+          <t>2588</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
@@ -11508,7 +11508,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,12%</t>
         </is>
       </c>
     </row>
@@ -11561,7 +11561,7 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>594</t>
+          <t>609</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
@@ -11571,12 +11571,12 @@
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>2953</t>
+          <t>3108</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
@@ -11586,7 +11586,7 @@
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,68%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -11596,7 +11596,7 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>594</t>
+          <t>609</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
@@ -11606,12 +11606,12 @@
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>2900</t>
+          <t>3689</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
@@ -11621,7 +11621,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>3,01%</t>
         </is>
       </c>
     </row>
@@ -11639,17 +11639,17 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>35606</t>
+          <t>37843</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>35606</t>
+          <t>37843</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>35606</t>
+          <t>37843</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -11674,17 +11674,17 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>79554</t>
+          <t>84521</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>79554</t>
+          <t>84521</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>79554</t>
+          <t>84521</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -11709,17 +11709,17 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>115160</t>
+          <t>122364</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>115160</t>
+          <t>122364</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>115160</t>
+          <t>122364</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -11756,32 +11756,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>13616</t>
+          <t>14448</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>7290</t>
+          <t>7698</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>24116</t>
+          <t>24157</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>10,47%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,61%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>17,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -11791,32 +11791,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>9057</t>
+          <t>10438</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5015</t>
+          <t>6127</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14292</t>
+          <t>16579</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>9,4%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>4,92%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>14,02%</t>
+          <t>14,93%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -11826,32 +11826,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>22673</t>
+          <t>24886</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>15295</t>
+          <t>16871</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>33556</t>
+          <t>37216</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>9,77%</t>
+          <t>9,91%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>6,59%</t>
+          <t>6,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>14,46%</t>
+          <t>14,81%</t>
         </is>
       </c>
     </row>
@@ -11869,32 +11869,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>18342</t>
+          <t>16857</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9737</t>
+          <t>8673</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>33070</t>
+          <t>28634</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>12,02%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>7,49%</t>
+          <t>6,19%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -11904,32 +11904,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>7032</t>
+          <t>7294</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2770</t>
+          <t>2989</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>18213</t>
+          <t>18150</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,57%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,72%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>17,86%</t>
+          <t>16,35%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -11939,32 +11939,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>25373</t>
+          <t>24151</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>14172</t>
+          <t>14367</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>41908</t>
+          <t>38652</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>10,94%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>6,11%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>15,38%</t>
         </is>
       </c>
     </row>
@@ -11982,32 +11982,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>62843</t>
+          <t>71279</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>50093</t>
+          <t>57813</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>76680</t>
+          <t>84793</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>48,33%</t>
+          <t>50,83%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>38,52%</t>
+          <t>41,23%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>58,97%</t>
+          <t>60,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -12017,32 +12017,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>63998</t>
+          <t>68573</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>54304</t>
+          <t>58529</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>73081</t>
+          <t>77120</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>62,77%</t>
+          <t>61,76%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>53,26%</t>
+          <t>52,72%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>71,68%</t>
+          <t>69,46%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -12052,32 +12052,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>126842</t>
+          <t>139852</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>111806</t>
+          <t>123540</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>143999</t>
+          <t>156836</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>54,67%</t>
+          <t>55,66%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>48,19%</t>
+          <t>49,17%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>62,07%</t>
+          <t>62,42%</t>
         </is>
       </c>
     </row>
@@ -12095,32 +12095,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>32677</t>
+          <t>33791</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>22573</t>
+          <t>23908</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>43466</t>
+          <t>47131</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>25,13%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>17,36%</t>
+          <t>17,05%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>33,42%</t>
+          <t>33,61%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -12130,32 +12130,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>17612</t>
+          <t>20366</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>12055</t>
+          <t>14313</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>25147</t>
+          <t>28957</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>17,27%</t>
+          <t>18,34%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,82%</t>
+          <t>12,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>24,66%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -12165,32 +12165,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>50289</t>
+          <t>54157</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>39672</t>
+          <t>41909</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>64953</t>
+          <t>67571</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>21,68%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>16,68%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>28,0%</t>
+          <t>26,89%</t>
         </is>
       </c>
     </row>
@@ -12208,7 +12208,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>1168</t>
+          <t>2429</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -12218,12 +12218,12 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>4697</t>
+          <t>8044</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
@@ -12233,7 +12233,7 @@
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -12243,32 +12243,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>4258</t>
+          <t>4356</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>1432</t>
+          <t>1482</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>11678</t>
+          <t>9981</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>4,18%</t>
+          <t>3,92%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>11,45%</t>
+          <t>8,99%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -12278,32 +12278,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>5426</t>
+          <t>6786</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>2050</t>
+          <t>2980</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>11756</t>
+          <t>14782</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>5,88%</t>
         </is>
       </c>
     </row>
@@ -12321,7 +12321,7 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>1396</t>
+          <t>1412</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
@@ -12331,12 +12331,12 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6741</t>
+          <t>7054</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -12346,7 +12346,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,18%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -12391,7 +12391,7 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>1396</t>
+          <t>1412</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
@@ -12401,12 +12401,12 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>6471</t>
+          <t>7166</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
@@ -12416,7 +12416,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,85%</t>
         </is>
       </c>
     </row>
@@ -12434,17 +12434,17 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>130042</t>
+          <t>140218</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>130042</t>
+          <t>140218</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>130042</t>
+          <t>140218</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -12469,17 +12469,17 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>101957</t>
+          <t>111027</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>101957</t>
+          <t>111027</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>101957</t>
+          <t>111027</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -12504,17 +12504,17 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>231999</t>
+          <t>251245</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>231999</t>
+          <t>251245</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>231999</t>
+          <t>251245</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -12551,32 +12551,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>8823</t>
+          <t>9267</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2834</t>
+          <t>2647</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>18223</t>
+          <t>20590</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>26,56%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>8,53%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>54,85%</t>
+          <t>49,41%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -12586,32 +12586,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>2465</t>
+          <t>2594</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>594</t>
+          <t>983</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>6205</t>
+          <t>6906</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>7,99%</t>
+          <t>7,36%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>2,79%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>20,1%</t>
+          <t>19,6%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -12621,32 +12621,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>11289</t>
+          <t>11861</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>4866</t>
+          <t>4731</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>22293</t>
+          <t>23640</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>17,61%</t>
+          <t>15,42%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>7,59%</t>
+          <t>6,15%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>34,78%</t>
+          <t>30,74%</t>
         </is>
       </c>
     </row>
@@ -12664,7 +12664,7 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>2256</t>
+          <t>2286</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
@@ -12674,12 +12674,12 @@
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>7509</t>
+          <t>6820</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
@@ -12689,7 +12689,7 @@
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>22,6%</t>
+          <t>16,37%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -12699,7 +12699,7 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>994</t>
+          <t>1087</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
@@ -12709,12 +12709,12 @@
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>4355</t>
+          <t>4090</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>3,22%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
@@ -12724,7 +12724,7 @@
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>14,11%</t>
+          <t>11,61%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -12734,32 +12734,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>3251</t>
+          <t>3372</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>917</t>
+          <t>707</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>8638</t>
+          <t>9132</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>5,07%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>13,48%</t>
+          <t>11,87%</t>
         </is>
       </c>
     </row>
@@ -12777,32 +12777,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>15271</t>
+          <t>22993</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>8543</t>
+          <t>14896</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>22578</t>
+          <t>31292</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>45,96%</t>
+          <t>55,18%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>25,71%</t>
+          <t>35,75%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>67,95%</t>
+          <t>75,1%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -12812,32 +12812,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>19072</t>
+          <t>22354</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>14320</t>
+          <t>17274</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>22958</t>
+          <t>26447</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>61,79%</t>
+          <t>63,44%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>46,39%</t>
+          <t>49,02%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>74,38%</t>
+          <t>75,05%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -12847,32 +12847,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>34343</t>
+          <t>45347</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>25954</t>
+          <t>35948</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>42377</t>
+          <t>54108</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>53,58%</t>
+          <t>58,96%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>40,49%</t>
+          <t>46,74%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>66,12%</t>
+          <t>70,35%</t>
         </is>
       </c>
     </row>
@@ -12890,32 +12890,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>5863</t>
+          <t>5981</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>2377</t>
+          <t>2442</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>11320</t>
+          <t>11391</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>5,86%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -12925,32 +12925,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>7551</t>
+          <t>8433</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>4184</t>
+          <t>4910</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>11477</t>
+          <t>13417</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>24,46%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,93%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>37,18%</t>
+          <t>38,08%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -12960,32 +12960,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>13415</t>
+          <t>14414</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>8991</t>
+          <t>8730</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>20309</t>
+          <t>21241</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>18,74%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>14,03%</t>
+          <t>11,35%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>31,69%</t>
+          <t>27,62%</t>
         </is>
       </c>
     </row>
@@ -13003,7 +13003,7 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>1012</t>
+          <t>1143</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
@@ -13013,12 +13013,12 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>5267</t>
+          <t>5775</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -13028,7 +13028,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>13,86%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -13038,7 +13038,7 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>783</t>
+          <t>772</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
@@ -13048,12 +13048,12 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3930</t>
+          <t>4628</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
@@ -13063,7 +13063,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>12,73%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -13073,7 +13073,7 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1795</t>
+          <t>1915</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
@@ -13083,12 +13083,12 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6216</t>
+          <t>7155</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,49%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
@@ -13098,7 +13098,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>9,7%</t>
+          <t>9,3%</t>
         </is>
       </c>
     </row>
@@ -13229,17 +13229,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>33226</t>
+          <t>41669</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>33226</t>
+          <t>41669</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>33226</t>
+          <t>41669</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -13264,17 +13264,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>30866</t>
+          <t>35239</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>30866</t>
+          <t>35239</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>30866</t>
+          <t>35239</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -13299,17 +13299,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>64092</t>
+          <t>76908</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>64092</t>
+          <t>76908</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>64092</t>
+          <t>76908</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -13346,32 +13346,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>27269</t>
+          <t>29047</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>17288</t>
+          <t>17792</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>42334</t>
+          <t>44180</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,22%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>8,69%</t>
+          <t>8,1%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>20,11%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -13381,32 +13381,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>18634</t>
+          <t>20764</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>12427</t>
+          <t>14663</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>26027</t>
+          <t>29657</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>9,0%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>5,85%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>12,26%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -13416,32 +13416,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>45904</t>
+          <t>49811</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>33515</t>
+          <t>37316</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>62309</t>
+          <t>65810</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>8,15%</t>
+          <t>8,28%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>15,15%</t>
+          <t>14,61%</t>
         </is>
       </c>
     </row>
@@ -13459,32 +13459,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>20944</t>
+          <t>19488</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>11761</t>
+          <t>12033</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>36988</t>
+          <t>32840</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>8,87%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>5,91%</t>
+          <t>5,48%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -13494,32 +13494,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>10977</t>
+          <t>11617</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>6181</t>
+          <t>6248</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>23312</t>
+          <t>24807</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,03%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>10,98%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -13529,32 +13529,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>31921</t>
+          <t>31105</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>20269</t>
+          <t>19610</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>50046</t>
+          <t>45880</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>7,76%</t>
+          <t>6,9%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>4,93%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>12,17%</t>
+          <t>10,18%</t>
         </is>
       </c>
     </row>
@@ -13572,32 +13572,32 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>98843</t>
+          <t>116188</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>82063</t>
+          <t>98891</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>114575</t>
+          <t>131650</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>49,7%</t>
+          <t>52,88%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>41,26%</t>
+          <t>45,01%</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>57,61%</t>
+          <t>59,91%</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
@@ -13607,32 +13607,32 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>134981</t>
+          <t>144952</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>122937</t>
+          <t>132357</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>146270</t>
+          <t>158168</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>63,56%</t>
+          <t>62,81%</t>
         </is>
       </c>
       <c r="O27" s="2" t="inlineStr">
         <is>
-          <t>57,89%</t>
+          <t>57,35%</t>
         </is>
       </c>
       <c r="P27" s="2" t="inlineStr">
         <is>
-          <t>68,87%</t>
+          <t>68,53%</t>
         </is>
       </c>
       <c r="Q27" s="2" t="inlineStr">
@@ -13642,32 +13642,32 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>233825</t>
+          <t>261140</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>216145</t>
+          <t>239540</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>254803</t>
+          <t>283256</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
         <is>
-          <t>56,86%</t>
+          <t>57,96%</t>
         </is>
       </c>
       <c r="V27" s="2" t="inlineStr">
         <is>
-          <t>52,56%</t>
+          <t>53,17%</t>
         </is>
       </c>
       <c r="W27" s="2" t="inlineStr">
         <is>
-          <t>61,96%</t>
+          <t>62,87%</t>
         </is>
       </c>
     </row>
@@ -13685,32 +13685,32 @@
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>48241</t>
+          <t>50021</t>
         </is>
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>36496</t>
+          <t>37692</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
         <is>
-          <t>61744</t>
+          <t>62924</t>
         </is>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>24,26%</t>
+          <t>22,77%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>18,35%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="I28" s="2" t="inlineStr">
         <is>
-          <t>31,05%</t>
+          <t>28,64%</t>
         </is>
       </c>
       <c r="J28" s="2" t="inlineStr">
@@ -13720,32 +13720,32 @@
       </c>
       <c r="K28" s="2" t="inlineStr">
         <is>
-          <t>41689</t>
+          <t>47210</t>
         </is>
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>33559</t>
+          <t>37298</t>
         </is>
       </c>
       <c r="M28" s="2" t="inlineStr">
         <is>
-          <t>50988</t>
+          <t>57195</t>
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr">
         <is>
-          <t>19,63%</t>
+          <t>20,46%</t>
         </is>
       </c>
       <c r="O28" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>16,16%</t>
         </is>
       </c>
       <c r="P28" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="Q28" s="2" t="inlineStr">
@@ -13755,32 +13755,32 @@
       </c>
       <c r="R28" s="2" t="inlineStr">
         <is>
-          <t>89929</t>
+          <t>97231</t>
         </is>
       </c>
       <c r="S28" s="2" t="inlineStr">
         <is>
-          <t>75392</t>
+          <t>80882</t>
         </is>
       </c>
       <c r="T28" s="2" t="inlineStr">
         <is>
-          <t>105818</t>
+          <t>113353</t>
         </is>
       </c>
       <c r="U28" s="2" t="inlineStr">
         <is>
-          <t>21,87%</t>
+          <t>21,58%</t>
         </is>
       </c>
       <c r="V28" s="2" t="inlineStr">
         <is>
-          <t>18,33%</t>
+          <t>17,95%</t>
         </is>
       </c>
       <c r="W28" s="2" t="inlineStr">
         <is>
-          <t>25,73%</t>
+          <t>25,16%</t>
         </is>
       </c>
     </row>
@@ -13798,32 +13798,32 @@
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>2180</t>
+          <t>3572</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>166</t>
+          <t>922</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>7791</t>
+          <t>10078</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="I29" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="J29" s="2" t="inlineStr">
@@ -13833,32 +13833,32 @@
       </c>
       <c r="K29" s="2" t="inlineStr">
         <is>
-          <t>5502</t>
+          <t>5637</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2259</t>
+          <t>2166</t>
         </is>
       </c>
       <c r="M29" s="2" t="inlineStr">
         <is>
-          <t>11397</t>
+          <t>11731</t>
         </is>
       </c>
       <c r="N29" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="O29" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P29" s="2" t="inlineStr">
         <is>
-          <t>5,37%</t>
+          <t>5,08%</t>
         </is>
       </c>
       <c r="Q29" s="2" t="inlineStr">
@@ -13868,32 +13868,32 @@
       </c>
       <c r="R29" s="2" t="inlineStr">
         <is>
-          <t>7682</t>
+          <t>9209</t>
         </is>
       </c>
       <c r="S29" s="2" t="inlineStr">
         <is>
-          <t>3641</t>
+          <t>4646</t>
         </is>
       </c>
       <c r="T29" s="2" t="inlineStr">
         <is>
-          <t>14432</t>
+          <t>16600</t>
         </is>
       </c>
       <c r="U29" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="V29" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W29" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,68%</t>
         </is>
       </c>
     </row>
@@ -13911,7 +13911,7 @@
       </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>1396</t>
+          <t>1412</t>
         </is>
       </c>
       <c r="E30" s="2" t="inlineStr">
@@ -13921,12 +13921,12 @@
       </c>
       <c r="F30" s="2" t="inlineStr">
         <is>
-          <t>7229</t>
+          <t>7529</t>
         </is>
       </c>
       <c r="G30" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -13936,7 +13936,7 @@
       </c>
       <c r="I30" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,43%</t>
         </is>
       </c>
       <c r="J30" s="2" t="inlineStr">
@@ -13946,7 +13946,7 @@
       </c>
       <c r="K30" s="2" t="inlineStr">
         <is>
-          <t>594</t>
+          <t>609</t>
         </is>
       </c>
       <c r="L30" s="2" t="inlineStr">
@@ -13956,12 +13956,12 @@
       </c>
       <c r="M30" s="2" t="inlineStr">
         <is>
-          <t>2908</t>
+          <t>3344</t>
         </is>
       </c>
       <c r="N30" s="2" t="inlineStr">
         <is>
-          <t>0,28%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="O30" s="2" t="inlineStr">
@@ -13971,7 +13971,7 @@
       </c>
       <c r="P30" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="Q30" s="2" t="inlineStr">
@@ -13981,7 +13981,7 @@
       </c>
       <c r="R30" s="2" t="inlineStr">
         <is>
-          <t>1990</t>
+          <t>2022</t>
         </is>
       </c>
       <c r="S30" s="2" t="inlineStr">
@@ -13991,12 +13991,12 @@
       </c>
       <c r="T30" s="2" t="inlineStr">
         <is>
-          <t>7937</t>
+          <t>8300</t>
         </is>
       </c>
       <c r="U30" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="V30" s="2" t="inlineStr">
@@ -14006,7 +14006,7 @@
       </c>
       <c r="W30" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -14024,17 +14024,17 @@
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>198874</t>
+          <t>219729</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>198874</t>
+          <t>219729</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>198874</t>
+          <t>219729</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
@@ -14059,17 +14059,17 @@
       </c>
       <c r="K31" s="2" t="inlineStr">
         <is>
-          <t>212377</t>
+          <t>230788</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>212377</t>
+          <t>230788</t>
         </is>
       </c>
       <c r="M31" s="2" t="inlineStr">
         <is>
-          <t>212377</t>
+          <t>230788</t>
         </is>
       </c>
       <c r="N31" s="2" t="inlineStr">
@@ -14094,17 +14094,17 @@
       </c>
       <c r="R31" s="2" t="inlineStr">
         <is>
-          <t>411252</t>
+          <t>450517</t>
         </is>
       </c>
       <c r="S31" s="2" t="inlineStr">
         <is>
-          <t>411252</t>
+          <t>450517</t>
         </is>
       </c>
       <c r="T31" s="2" t="inlineStr">
         <is>
-          <t>411252</t>
+          <t>450517</t>
         </is>
       </c>
       <c r="U31" s="2" t="inlineStr">
